--- a/research/traditional_assets/database/data/oman/oman_steel.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_steel.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1211125356863123</v>
+        <v>0.1209691168827828</v>
       </c>
       <c r="C2">
-        <v>223.2648634632929</v>
+        <v>221.6221894543159</v>
       </c>
       <c r="D2">
-        <v>212.9648634632929</v>
+        <v>213.3711894543159</v>
       </c>
       <c r="E2">
-        <v>-111.1</v>
+        <v>-109.051</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.049</v>
       </c>
       <c r="G2">
         <v>10.3</v>
@@ -1451,28 +1451,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1030647</v>
       </c>
       <c r="N2">
-        <v>21.29591836734694</v>
+        <v>21.19285366734694</v>
       </c>
       <c r="O2">
-        <v>3.194387755102041</v>
+        <v>3.178928050102041</v>
       </c>
       <c r="P2">
-        <v>18.1015306122449</v>
+        <v>18.0139256172449</v>
       </c>
       <c r="Q2">
-        <v>21.6015306122449</v>
+        <v>21.5139256172449</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1211125356863123</v>
+        <v>0.1217591584674574</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161358</v>
+        <v>0.990002472828951</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>206.6266953413432</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1209691168827828</v>
+        <v>0.1208256980792533</v>
       </c>
       <c r="C3">
-        <v>221.6221894543159</v>
+        <v>219.9810689073917</v>
       </c>
       <c r="D3">
-        <v>213.3711894543159</v>
+        <v>213.7790689073917</v>
       </c>
       <c r="E3">
-        <v>-109.051</v>
+        <v>-107.002</v>
       </c>
       <c r="F3">
-        <v>2.049</v>
+        <v>4.098</v>
       </c>
       <c r="G3">
         <v>10.3</v>
@@ -1533,28 +1533,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M3">
-        <v>0.1030647</v>
+        <v>0.2061294</v>
       </c>
       <c r="N3">
-        <v>21.19285366734694</v>
+        <v>21.08978896734694</v>
       </c>
       <c r="O3">
-        <v>3.178928050102041</v>
+        <v>3.163468345102041</v>
       </c>
       <c r="P3">
-        <v>18.0139256172449</v>
+        <v>17.9263206222449</v>
       </c>
       <c r="Q3">
-        <v>21.5139256172449</v>
+        <v>21.4263206222449</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1217591584674574</v>
+        <v>0.1224189776318911</v>
       </c>
       <c r="T3">
-        <v>0.990002472828951</v>
+        <v>0.998602128454273</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>206.6266953413432</v>
+        <v>103.3133476706716</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1208256980792533</v>
+        <v>0.1206822792757238</v>
       </c>
       <c r="C4">
-        <v>219.9810689073917</v>
+        <v>218.3415107483573</v>
       </c>
       <c r="D4">
-        <v>213.7790689073917</v>
+        <v>214.1885107483572</v>
       </c>
       <c r="E4">
-        <v>-107.002</v>
+        <v>-104.953</v>
       </c>
       <c r="F4">
-        <v>4.098</v>
+        <v>6.146999999999999</v>
       </c>
       <c r="G4">
         <v>10.3</v>
@@ -1615,28 +1615,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M4">
-        <v>0.2061294</v>
+        <v>0.3091941</v>
       </c>
       <c r="N4">
-        <v>21.08978896734694</v>
+        <v>20.98672426734694</v>
       </c>
       <c r="O4">
-        <v>3.163468345102041</v>
+        <v>3.148008640102041</v>
       </c>
       <c r="P4">
-        <v>17.9263206222449</v>
+        <v>17.8387156272449</v>
       </c>
       <c r="Q4">
-        <v>21.4263206222449</v>
+        <v>21.3387156272449</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1224189776318911</v>
+        <v>0.1230924013151792</v>
       </c>
       <c r="T4">
-        <v>0.998602128454273</v>
+        <v>1.007379096566715</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>103.3133476706716</v>
+        <v>68.87556511378109</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1206822792757238</v>
+        <v>0.1205388604721944</v>
       </c>
       <c r="C5">
-        <v>218.3415107483573</v>
+        <v>216.7035239715615</v>
       </c>
       <c r="D5">
-        <v>214.1885107483572</v>
+        <v>214.5995239715614</v>
       </c>
       <c r="E5">
-        <v>-104.953</v>
+        <v>-102.904</v>
       </c>
       <c r="F5">
-        <v>6.146999999999999</v>
+        <v>8.196</v>
       </c>
       <c r="G5">
         <v>10.3</v>
@@ -1697,28 +1697,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M5">
-        <v>0.3091941</v>
+        <v>0.4122588</v>
       </c>
       <c r="N5">
-        <v>20.98672426734694</v>
+        <v>20.88365956734694</v>
       </c>
       <c r="O5">
-        <v>3.148008640102041</v>
+        <v>3.132548935102041</v>
       </c>
       <c r="P5">
-        <v>17.8387156272449</v>
+        <v>17.7511106322449</v>
       </c>
       <c r="Q5">
-        <v>21.3387156272449</v>
+        <v>21.2511106322449</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1230924013151792</v>
+        <v>0.1237798546585358</v>
       </c>
       <c r="T5">
-        <v>1.007379096566715</v>
+        <v>1.016338918181499</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>68.87556511378109</v>
+        <v>51.65667383533582</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1205388604721944</v>
+        <v>0.1203954416686649</v>
       </c>
       <c r="C6">
-        <v>216.7035239715615</v>
+        <v>215.0671176405245</v>
       </c>
       <c r="D6">
-        <v>214.5995239715614</v>
+        <v>215.0121176405245</v>
       </c>
       <c r="E6">
-        <v>-102.904</v>
+        <v>-100.855</v>
       </c>
       <c r="F6">
-        <v>8.196</v>
+        <v>10.245</v>
       </c>
       <c r="G6">
         <v>10.3</v>
@@ -1779,28 +1779,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M6">
-        <v>0.4122588</v>
+        <v>0.5153234999999999</v>
       </c>
       <c r="N6">
-        <v>20.88365956734694</v>
+        <v>20.78059486734694</v>
       </c>
       <c r="O6">
-        <v>3.132548935102041</v>
+        <v>3.117089230102041</v>
       </c>
       <c r="P6">
-        <v>17.7511106322449</v>
+        <v>17.6635056372449</v>
       </c>
       <c r="Q6">
-        <v>21.2511106322449</v>
+        <v>21.1635056372449</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1237798546585358</v>
+        <v>0.1244817807038578</v>
       </c>
       <c r="T6">
-        <v>1.016338918181499</v>
+        <v>1.025487367619752</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.65667383533582</v>
+        <v>41.32533906826865</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1203954416686649</v>
+        <v>0.1202520228651354</v>
       </c>
       <c r="C7">
-        <v>215.0671176405245</v>
+        <v>213.4323008886036</v>
       </c>
       <c r="D7">
-        <v>215.0121176405245</v>
+        <v>215.4263008886036</v>
       </c>
       <c r="E7">
-        <v>-100.855</v>
+        <v>-98.806</v>
       </c>
       <c r="F7">
-        <v>10.245</v>
+        <v>12.294</v>
       </c>
       <c r="G7">
         <v>10.3</v>
@@ -1861,28 +1861,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M7">
-        <v>0.5153234999999999</v>
+        <v>0.6183881999999999</v>
       </c>
       <c r="N7">
-        <v>20.78059486734694</v>
+        <v>20.67753016734694</v>
       </c>
       <c r="O7">
-        <v>3.117089230102041</v>
+        <v>3.101629525102041</v>
       </c>
       <c r="P7">
-        <v>17.6635056372449</v>
+        <v>17.5759006422449</v>
       </c>
       <c r="Q7">
-        <v>21.1635056372449</v>
+        <v>21.0759006422449</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1244817807038578</v>
+        <v>0.1251986413458888</v>
       </c>
       <c r="T7">
-        <v>1.025487367619752</v>
+        <v>1.034830464918394</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>41.32533906826865</v>
+        <v>34.43778255689055</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1202520228651354</v>
+        <v>0.120108604061606</v>
       </c>
       <c r="C8">
-        <v>213.4323008886036</v>
+        <v>211.799082919667</v>
       </c>
       <c r="D8">
-        <v>215.4263008886036</v>
+        <v>215.842082919667</v>
       </c>
       <c r="E8">
-        <v>-98.806</v>
+        <v>-96.75700000000001</v>
       </c>
       <c r="F8">
-        <v>12.294</v>
+        <v>14.343</v>
       </c>
       <c r="G8">
         <v>10.3</v>
@@ -1943,28 +1943,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M8">
-        <v>0.6183881999999999</v>
+        <v>0.7214528999999997</v>
       </c>
       <c r="N8">
-        <v>20.67753016734694</v>
+        <v>20.57446546734694</v>
       </c>
       <c r="O8">
-        <v>3.101629525102041</v>
+        <v>3.086169820102041</v>
       </c>
       <c r="P8">
-        <v>17.5759006422449</v>
+        <v>17.4882956472449</v>
       </c>
       <c r="Q8">
-        <v>21.0759006422449</v>
+        <v>20.9882956472449</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1251986413458888</v>
+        <v>0.1259309183458129</v>
       </c>
       <c r="T8">
-        <v>1.034830464918394</v>
+        <v>1.044374489040663</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.43778255689055</v>
+        <v>29.51809933447762</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.120108604061606</v>
+        <v>0.1199651852580765</v>
       </c>
       <c r="C9">
-        <v>211.7990829196671</v>
+        <v>210.1674730087759</v>
       </c>
       <c r="D9">
-        <v>215.842082919667</v>
+        <v>216.2594730087759</v>
       </c>
       <c r="E9">
-        <v>-96.75699999999999</v>
+        <v>-94.708</v>
       </c>
       <c r="F9">
-        <v>14.343</v>
+        <v>16.392</v>
       </c>
       <c r="G9">
         <v>10.3</v>
@@ -2025,28 +2025,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M9">
-        <v>0.7214529</v>
+        <v>0.8245176</v>
       </c>
       <c r="N9">
-        <v>20.57446546734694</v>
+        <v>20.47140076734694</v>
       </c>
       <c r="O9">
-        <v>3.086169820102041</v>
+        <v>3.070710115102041</v>
       </c>
       <c r="P9">
-        <v>17.4882956472449</v>
+        <v>17.4006906522449</v>
       </c>
       <c r="Q9">
-        <v>20.9882956472449</v>
+        <v>20.9006906522449</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1259309183458129</v>
+        <v>0.1266791144109527</v>
       </c>
       <c r="T9">
-        <v>1.044374489040663</v>
+        <v>1.054125991948198</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.51809933447761</v>
+        <v>25.82833691766791</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1199651852580765</v>
+        <v>0.119821766454547</v>
       </c>
       <c r="C10">
-        <v>210.1674730087759</v>
+        <v>208.537480502874</v>
       </c>
       <c r="D10">
-        <v>216.2594730087759</v>
+        <v>216.678480502874</v>
       </c>
       <c r="E10">
-        <v>-94.708</v>
+        <v>-92.65899999999999</v>
       </c>
       <c r="F10">
-        <v>16.392</v>
+        <v>18.441</v>
       </c>
       <c r="G10">
         <v>10.3</v>
@@ -2107,28 +2107,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M10">
-        <v>0.8245176</v>
+        <v>0.9275822999999999</v>
       </c>
       <c r="N10">
-        <v>20.47140076734694</v>
+        <v>20.36833606734694</v>
       </c>
       <c r="O10">
-        <v>3.070710115102041</v>
+        <v>3.055250410102041</v>
       </c>
       <c r="P10">
-        <v>17.4006906522449</v>
+        <v>17.3130856572449</v>
       </c>
       <c r="Q10">
-        <v>20.9006906522449</v>
+        <v>20.8130856572449</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1266791144109527</v>
+        <v>0.1274437543456561</v>
       </c>
       <c r="T10">
-        <v>1.054125991948198</v>
+        <v>1.064091813600954</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.82833691766791</v>
+        <v>22.9585217045937</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.119821766454547</v>
+        <v>0.1196783476510176</v>
       </c>
       <c r="C11">
-        <v>208.537480502874</v>
+        <v>206.9091148214852</v>
       </c>
       <c r="D11">
-        <v>216.678480502874</v>
+        <v>217.0991148214852</v>
       </c>
       <c r="E11">
-        <v>-92.65899999999999</v>
+        <v>-90.61</v>
       </c>
       <c r="F11">
-        <v>18.441</v>
+        <v>20.48999999999999</v>
       </c>
       <c r="G11">
         <v>10.3</v>
@@ -2189,28 +2189,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M11">
-        <v>0.9275822999999999</v>
+        <v>1.030647</v>
       </c>
       <c r="N11">
-        <v>20.36833606734694</v>
+        <v>20.26527136734694</v>
       </c>
       <c r="O11">
-        <v>3.055250410102041</v>
+        <v>3.039790705102041</v>
       </c>
       <c r="P11">
-        <v>17.3130856572449</v>
+        <v>17.2254806622449</v>
       </c>
       <c r="Q11">
-        <v>20.8130856572449</v>
+        <v>20.7254806622449</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1274437543456561</v>
+        <v>0.1282253862789084</v>
       </c>
       <c r="T11">
-        <v>1.064091813600954</v>
+        <v>1.074279097957104</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.9585217045937</v>
+        <v>20.66266953413433</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1196783476510176</v>
+        <v>0.1195349288474881</v>
       </c>
       <c r="C12">
-        <v>206.9091148214852</v>
+        <v>205.2823854574195</v>
       </c>
       <c r="D12">
-        <v>217.0991148214852</v>
+        <v>217.5213854574195</v>
       </c>
       <c r="E12">
-        <v>-90.61</v>
+        <v>-88.56099999999999</v>
       </c>
       <c r="F12">
-        <v>20.49</v>
+        <v>22.539</v>
       </c>
       <c r="G12">
         <v>10.3</v>
@@ -2271,28 +2271,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M12">
-        <v>1.030647</v>
+        <v>1.1337117</v>
       </c>
       <c r="N12">
-        <v>20.26527136734694</v>
+        <v>20.16220666734694</v>
       </c>
       <c r="O12">
-        <v>3.039790705102041</v>
+        <v>3.024331000102041</v>
       </c>
       <c r="P12">
-        <v>17.2254806622449</v>
+        <v>17.1378756672449</v>
       </c>
       <c r="Q12">
-        <v>20.7254806622449</v>
+        <v>20.6378756672449</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1282253862789084</v>
+        <v>0.1290245829747057</v>
       </c>
       <c r="T12">
-        <v>1.074279097957104</v>
+        <v>1.084695310051595</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.66266953413433</v>
+        <v>18.78424503103121</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1195349288474881</v>
+        <v>0.1193915100439586</v>
       </c>
       <c r="C13">
-        <v>205.2823854574195</v>
+        <v>203.6573019774874</v>
       </c>
       <c r="D13">
-        <v>217.5213854574195</v>
+        <v>217.9453019774874</v>
       </c>
       <c r="E13">
-        <v>-88.56099999999999</v>
+        <v>-86.512</v>
       </c>
       <c r="F13">
-        <v>22.539</v>
+        <v>24.588</v>
       </c>
       <c r="G13">
         <v>10.3</v>
@@ -2353,28 +2353,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M13">
-        <v>1.1337117</v>
+        <v>1.2367764</v>
       </c>
       <c r="N13">
-        <v>20.16220666734694</v>
+        <v>20.05914196734694</v>
       </c>
       <c r="O13">
-        <v>3.024331000102041</v>
+        <v>3.008871295102041</v>
       </c>
       <c r="P13">
-        <v>17.1378756672449</v>
+        <v>17.0502706722449</v>
       </c>
       <c r="Q13">
-        <v>20.6378756672449</v>
+        <v>20.5502706722449</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1290245829747057</v>
+        <v>0.1298419432317712</v>
       </c>
       <c r="T13">
-        <v>1.084695310051595</v>
+        <v>1.095348254239143</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.78424503103121</v>
+        <v>17.21889127844527</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1193915100439586</v>
+        <v>0.1192480912404291</v>
       </c>
       <c r="C14">
-        <v>203.6573019774874</v>
+        <v>202.0338740232219</v>
       </c>
       <c r="D14">
-        <v>217.9453019774874</v>
+        <v>218.3708740232219</v>
       </c>
       <c r="E14">
-        <v>-86.512</v>
+        <v>-84.46299999999999</v>
       </c>
       <c r="F14">
-        <v>24.588</v>
+        <v>26.637</v>
       </c>
       <c r="G14">
         <v>10.3</v>
@@ -2435,28 +2435,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M14">
-        <v>1.2367764</v>
+        <v>1.3398411</v>
       </c>
       <c r="N14">
-        <v>20.05914196734694</v>
+        <v>19.95607726734694</v>
       </c>
       <c r="O14">
-        <v>3.008871295102041</v>
+        <v>2.993411590102041</v>
       </c>
       <c r="P14">
-        <v>17.0502706722449</v>
+        <v>16.9626656772449</v>
       </c>
       <c r="Q14">
-        <v>20.5502706722449</v>
+        <v>20.4626656772449</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1298419432317712</v>
+        <v>0.1306780933798036</v>
       </c>
       <c r="T14">
-        <v>1.095348254239143</v>
+        <v>1.106246093695369</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.21889127844527</v>
+        <v>15.89436118010333</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1192480912404291</v>
+        <v>0.1191046724368997</v>
       </c>
       <c r="C15">
-        <v>202.0338740232219</v>
+        <v>200.4121113116097</v>
       </c>
       <c r="D15">
-        <v>218.3708740232219</v>
+        <v>218.7981113116097</v>
       </c>
       <c r="E15">
-        <v>-84.46299999999999</v>
+        <v>-82.41399999999999</v>
       </c>
       <c r="F15">
-        <v>26.637</v>
+        <v>28.686</v>
       </c>
       <c r="G15">
         <v>10.3</v>
@@ -2517,28 +2517,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M15">
-        <v>1.3398411</v>
+        <v>1.4429058</v>
       </c>
       <c r="N15">
-        <v>19.95607726734694</v>
+        <v>19.85301256734694</v>
       </c>
       <c r="O15">
-        <v>2.993411590102041</v>
+        <v>2.977951885102041</v>
       </c>
       <c r="P15">
-        <v>16.9626656772449</v>
+        <v>16.8750606822449</v>
       </c>
       <c r="Q15">
-        <v>20.4626656772449</v>
+        <v>20.3750606822449</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1306780933798036</v>
+        <v>0.1315336888801159</v>
       </c>
       <c r="T15">
-        <v>1.106246093695369</v>
+        <v>1.117397371278485</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.89436118010333</v>
+        <v>14.75904966723881</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1191046724368997</v>
+        <v>0.1189612536333702</v>
       </c>
       <c r="C16">
-        <v>200.4121113116097</v>
+        <v>198.7920236358308</v>
       </c>
       <c r="D16">
-        <v>218.7981113116097</v>
+        <v>219.2270236358308</v>
       </c>
       <c r="E16">
-        <v>-82.41399999999999</v>
+        <v>-80.36499999999999</v>
       </c>
       <c r="F16">
-        <v>28.686</v>
+        <v>30.735</v>
       </c>
       <c r="G16">
         <v>10.3</v>
@@ -2599,28 +2599,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M16">
-        <v>1.4429058</v>
+        <v>1.5459705</v>
       </c>
       <c r="N16">
-        <v>19.85301256734694</v>
+        <v>19.74994786734694</v>
       </c>
       <c r="O16">
-        <v>2.977951885102041</v>
+        <v>2.962492180102041</v>
       </c>
       <c r="P16">
-        <v>16.8750606822449</v>
+        <v>16.7874556872449</v>
       </c>
       <c r="Q16">
-        <v>20.3750606822449</v>
+        <v>20.2874556872449</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1315336888801159</v>
+        <v>0.1324094160392591</v>
       </c>
       <c r="T16">
-        <v>1.117397371278485</v>
+        <v>1.128811031863556</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.75904966723881</v>
+        <v>13.77511302275622</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1189612536333702</v>
+        <v>0.1188178348298407</v>
       </c>
       <c r="C17">
-        <v>198.7920236358308</v>
+        <v>197.1736208660068</v>
       </c>
       <c r="D17">
-        <v>219.2270236358308</v>
+        <v>219.6576208660067</v>
       </c>
       <c r="E17">
-        <v>-80.36499999999999</v>
+        <v>-78.316</v>
       </c>
       <c r="F17">
-        <v>30.735</v>
+        <v>32.784</v>
       </c>
       <c r="G17">
         <v>10.3</v>
@@ -2681,28 +2681,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M17">
-        <v>1.5459705</v>
+        <v>1.6490352</v>
       </c>
       <c r="N17">
-        <v>19.74994786734694</v>
+        <v>19.64688316734694</v>
       </c>
       <c r="O17">
-        <v>2.962492180102041</v>
+        <v>2.947032475102041</v>
       </c>
       <c r="P17">
-        <v>16.7874556872449</v>
+        <v>16.6998506922449</v>
       </c>
       <c r="Q17">
-        <v>20.2874556872449</v>
+        <v>20.1998506922449</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1324094160392591</v>
+        <v>0.1333059938450485</v>
       </c>
       <c r="T17">
-        <v>1.128811031863556</v>
+        <v>1.140496446272082</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>13.77511302275622</v>
+        <v>12.91416845883395</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1188178348298407</v>
+        <v>0.1188911660263113</v>
       </c>
       <c r="C18">
-        <v>197.1736208660068</v>
+        <v>194.9042418923538</v>
       </c>
       <c r="D18">
-        <v>219.6576208660067</v>
+        <v>219.4372418923538</v>
       </c>
       <c r="E18">
-        <v>-78.316</v>
+        <v>-76.267</v>
       </c>
       <c r="F18">
-        <v>32.784</v>
+        <v>34.833</v>
       </c>
       <c r="G18">
         <v>10.3</v>
@@ -2763,45 +2763,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M18">
-        <v>1.6490352</v>
+        <v>1.8043494</v>
       </c>
       <c r="N18">
-        <v>19.64688316734694</v>
+        <v>19.49156896734694</v>
       </c>
       <c r="O18">
-        <v>2.947032475102041</v>
+        <v>2.923735345102041</v>
       </c>
       <c r="P18">
-        <v>16.6998506922449</v>
+        <v>16.5678336222449</v>
       </c>
       <c r="Q18">
-        <v>20.1998506922449</v>
+        <v>20.0678336222449</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1333059938450485</v>
+        <v>0.1342241759353148</v>
       </c>
       <c r="T18">
-        <v>1.140496446272082</v>
+        <v>1.152463436931415</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.15</v>
       </c>
       <c r="W18">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>12.91416845883395</v>
+        <v>11.80254687221164</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1188911660263113</v>
+        <v>0.1187604972227818</v>
       </c>
       <c r="C19">
-        <v>194.9042418923538</v>
+        <v>193.2482436253372</v>
       </c>
       <c r="D19">
-        <v>219.4372418923538</v>
+        <v>219.8302436253372</v>
       </c>
       <c r="E19">
-        <v>-76.267</v>
+        <v>-74.21799999999999</v>
       </c>
       <c r="F19">
-        <v>34.833</v>
+        <v>36.882</v>
       </c>
       <c r="G19">
         <v>10.3</v>
@@ -2845,28 +2845,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M19">
-        <v>1.8043494</v>
+        <v>1.9104876</v>
       </c>
       <c r="N19">
-        <v>19.49156896734694</v>
+        <v>19.38543076734694</v>
       </c>
       <c r="O19">
-        <v>2.923735345102041</v>
+        <v>2.907814615102041</v>
       </c>
       <c r="P19">
-        <v>16.5678336222449</v>
+        <v>16.4776161522449</v>
       </c>
       <c r="Q19">
-        <v>20.0678336222449</v>
+        <v>19.9776161522449</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1342241759353148</v>
+        <v>0.1351647527107095</v>
       </c>
       <c r="T19">
-        <v>1.152463436931415</v>
+        <v>1.164722305411708</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.80254687221164</v>
+        <v>11.14684982375543</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1187604972227818</v>
+        <v>0.1186298284192524</v>
       </c>
       <c r="C20">
-        <v>193.2482436253372</v>
+        <v>191.5936555790322</v>
       </c>
       <c r="D20">
-        <v>219.8302436253371</v>
+        <v>220.2246555790322</v>
       </c>
       <c r="E20">
-        <v>-74.21799999999999</v>
+        <v>-72.169</v>
       </c>
       <c r="F20">
-        <v>36.882</v>
+        <v>38.931</v>
       </c>
       <c r="G20">
         <v>10.3</v>
@@ -2927,28 +2927,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M20">
-        <v>1.9104876</v>
+        <v>2.0166258</v>
       </c>
       <c r="N20">
-        <v>19.38543076734694</v>
+        <v>19.27929256734694</v>
       </c>
       <c r="O20">
-        <v>2.907814615102041</v>
+        <v>2.891893885102041</v>
       </c>
       <c r="P20">
-        <v>16.4776161522449</v>
+        <v>16.3873986822449</v>
       </c>
       <c r="Q20">
-        <v>19.9776161522449</v>
+        <v>19.8873986822449</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1351647527107095</v>
+        <v>0.1361285536040152</v>
       </c>
       <c r="T20">
-        <v>1.164722305411708</v>
+        <v>1.177283862002624</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.14684982375543</v>
+        <v>10.56017351724199</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1186298284192524</v>
+        <v>0.1184991596157229</v>
       </c>
       <c r="C21">
-        <v>191.5936555790322</v>
+        <v>189.9404853575925</v>
       </c>
       <c r="D21">
-        <v>220.2246555790322</v>
+        <v>220.6204853575925</v>
       </c>
       <c r="E21">
-        <v>-72.169</v>
+        <v>-70.12</v>
       </c>
       <c r="F21">
-        <v>38.931</v>
+        <v>40.98</v>
       </c>
       <c r="G21">
         <v>10.3</v>
@@ -3009,28 +3009,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M21">
-        <v>2.0166258</v>
+        <v>2.122764</v>
       </c>
       <c r="N21">
-        <v>19.27929256734694</v>
+        <v>19.17315436734694</v>
       </c>
       <c r="O21">
-        <v>2.891893885102041</v>
+        <v>2.875973155102041</v>
       </c>
       <c r="P21">
-        <v>16.3873986822449</v>
+        <v>16.2971812122449</v>
       </c>
       <c r="Q21">
-        <v>19.8873986822449</v>
+        <v>19.7971812122449</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1361285536040152</v>
+        <v>0.1371164495196536</v>
       </c>
       <c r="T21">
-        <v>1.177283862002624</v>
+        <v>1.190159457508315</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.56017351724199</v>
+        <v>10.03216484137989</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1184991596157229</v>
+        <v>0.1186719408121934</v>
       </c>
       <c r="C22">
-        <v>189.9404853575925</v>
+        <v>187.3683886621958</v>
       </c>
       <c r="D22">
-        <v>220.6204853575925</v>
+        <v>220.0973886621958</v>
       </c>
       <c r="E22">
-        <v>-70.12</v>
+        <v>-68.071</v>
       </c>
       <c r="F22">
-        <v>40.98</v>
+        <v>43.029</v>
       </c>
       <c r="G22">
         <v>10.3</v>
@@ -3091,45 +3091,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M22">
-        <v>2.122764</v>
+        <v>2.3020515</v>
       </c>
       <c r="N22">
-        <v>19.17315436734694</v>
+        <v>18.99386686734694</v>
       </c>
       <c r="O22">
-        <v>2.875973155102041</v>
+        <v>2.849080030102041</v>
       </c>
       <c r="P22">
-        <v>16.2971812122449</v>
+        <v>16.1447868372449</v>
       </c>
       <c r="Q22">
-        <v>19.7971812122449</v>
+        <v>19.6447868372449</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1371164495196536</v>
+        <v>0.1381293554584727</v>
       </c>
       <c r="T22">
-        <v>1.190159457508315</v>
+        <v>1.203361017457187</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.15</v>
       </c>
       <c r="W22">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>10.03216484137989</v>
+        <v>9.250843592051238</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1186719408121934</v>
+        <v>0.1185557220086639</v>
       </c>
       <c r="C23">
-        <v>187.3683886621959</v>
+        <v>185.6709686405682</v>
       </c>
       <c r="D23">
-        <v>220.0973886621958</v>
+        <v>220.4489686405682</v>
       </c>
       <c r="E23">
-        <v>-68.071</v>
+        <v>-66.02199999999999</v>
       </c>
       <c r="F23">
-        <v>43.029</v>
+        <v>45.078</v>
       </c>
       <c r="G23">
         <v>10.3</v>
@@ -3173,28 +3173,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M23">
-        <v>2.3020515</v>
+        <v>2.411673</v>
       </c>
       <c r="N23">
-        <v>18.99386686734694</v>
+        <v>18.88424536734694</v>
       </c>
       <c r="O23">
-        <v>2.849080030102041</v>
+        <v>2.832636805102041</v>
       </c>
       <c r="P23">
-        <v>16.1447868372449</v>
+        <v>16.0516085622449</v>
       </c>
       <c r="Q23">
-        <v>19.6447868372449</v>
+        <v>19.5516085622449</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1381293554584727</v>
+        <v>0.139168233344441</v>
       </c>
       <c r="T23">
-        <v>1.203361017457187</v>
+        <v>1.216901078943209</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.250843592051238</v>
+        <v>8.830350701503455</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1185557220086639</v>
+        <v>0.1184395032051345</v>
       </c>
       <c r="C24">
-        <v>185.6709686405682</v>
+        <v>183.9746736322635</v>
       </c>
       <c r="D24">
-        <v>220.4489686405682</v>
+        <v>220.8016736322635</v>
       </c>
       <c r="E24">
-        <v>-66.02199999999999</v>
+        <v>-63.973</v>
       </c>
       <c r="F24">
-        <v>45.078</v>
+        <v>47.127</v>
       </c>
       <c r="G24">
         <v>10.3</v>
@@ -3255,28 +3255,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M24">
-        <v>2.411673</v>
+        <v>2.5212945</v>
       </c>
       <c r="N24">
-        <v>18.88424536734694</v>
+        <v>18.77462386734694</v>
       </c>
       <c r="O24">
-        <v>2.832636805102041</v>
+        <v>2.816193580102041</v>
       </c>
       <c r="P24">
-        <v>16.0516085622449</v>
+        <v>15.9584302872449</v>
       </c>
       <c r="Q24">
-        <v>19.5516085622449</v>
+        <v>19.4584302872449</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.139168233344441</v>
+        <v>0.1402340950716032</v>
       </c>
       <c r="T24">
-        <v>1.216901078943209</v>
+        <v>1.23079283033796</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.830350701503455</v>
+        <v>8.446422410133739</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1184395032051345</v>
+        <v>0.118323284401605</v>
       </c>
       <c r="C25">
-        <v>183.9746736322635</v>
+        <v>182.2795090457942</v>
       </c>
       <c r="D25">
-        <v>220.8016736322635</v>
+        <v>221.1555090457942</v>
       </c>
       <c r="E25">
-        <v>-63.973</v>
+        <v>-61.92399999999999</v>
       </c>
       <c r="F25">
-        <v>47.127</v>
+        <v>49.176</v>
       </c>
       <c r="G25">
         <v>10.3</v>
@@ -3337,28 +3337,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M25">
-        <v>2.5212945</v>
+        <v>2.630916</v>
       </c>
       <c r="N25">
-        <v>18.77462386734694</v>
+        <v>18.66500236734694</v>
       </c>
       <c r="O25">
-        <v>2.816193580102041</v>
+        <v>2.799750355102041</v>
       </c>
       <c r="P25">
-        <v>15.9584302872449</v>
+        <v>15.8652520122449</v>
       </c>
       <c r="Q25">
-        <v>19.4584302872449</v>
+        <v>19.3652520122449</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1402340950716032</v>
+        <v>0.1413280057915855</v>
       </c>
       <c r="T25">
-        <v>1.23079283033796</v>
+        <v>1.245050154137835</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.446422410133739</v>
+        <v>8.094488143044833</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.118323284401605</v>
+        <v>0.1182070655980755</v>
       </c>
       <c r="C26">
-        <v>182.2795090457942</v>
+        <v>180.5854803243974</v>
       </c>
       <c r="D26">
-        <v>221.1555090457942</v>
+        <v>221.5104803243974</v>
       </c>
       <c r="E26">
-        <v>-61.924</v>
+        <v>-59.875</v>
       </c>
       <c r="F26">
-        <v>49.17599999999999</v>
+        <v>51.22499999999999</v>
       </c>
       <c r="G26">
         <v>10.3</v>
@@ -3419,28 +3419,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M26">
-        <v>2.630916</v>
+        <v>2.7405375</v>
       </c>
       <c r="N26">
-        <v>18.66500236734694</v>
+        <v>18.55538086734694</v>
       </c>
       <c r="O26">
-        <v>2.799750355102041</v>
+        <v>2.783307130102041</v>
       </c>
       <c r="P26">
-        <v>15.8652520122449</v>
+        <v>15.7720737372449</v>
       </c>
       <c r="Q26">
-        <v>19.3652520122449</v>
+        <v>19.2720737372449</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1413280057915855</v>
+        <v>0.1424510874641007</v>
       </c>
       <c r="T26">
-        <v>1.245050154137835</v>
+        <v>1.259687673239041</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.094488143044835</v>
+        <v>7.770708617323041</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1182070655980755</v>
+        <v>0.1182676467945461</v>
       </c>
       <c r="C27">
-        <v>180.5854803243974</v>
+        <v>178.3513029311413</v>
       </c>
       <c r="D27">
-        <v>221.5104803243974</v>
+        <v>221.3253029311413</v>
       </c>
       <c r="E27">
-        <v>-59.875</v>
+        <v>-57.826</v>
       </c>
       <c r="F27">
-        <v>51.22499999999999</v>
+        <v>53.27399999999999</v>
       </c>
       <c r="G27">
         <v>10.3</v>
@@ -3501,45 +3501,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M27">
-        <v>2.7405375</v>
+        <v>2.8927782</v>
       </c>
       <c r="N27">
-        <v>18.55538086734694</v>
+        <v>18.40314016734694</v>
       </c>
       <c r="O27">
-        <v>2.783307130102041</v>
+        <v>2.760471025102041</v>
       </c>
       <c r="P27">
-        <v>15.7720737372449</v>
+        <v>15.6426691422449</v>
       </c>
       <c r="Q27">
-        <v>19.2720737372449</v>
+        <v>19.1426691422449</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1424510874641007</v>
+        <v>0.1436045226953325</v>
       </c>
       <c r="T27">
-        <v>1.259687673239041</v>
+        <v>1.274720800964603</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.770708617323041</v>
+        <v>7.36175292227622</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1182676467945461</v>
+        <v>0.1181582279910166</v>
       </c>
       <c r="C28">
-        <v>178.3513029311413</v>
+        <v>176.6369870508316</v>
       </c>
       <c r="D28">
-        <v>221.3253029311413</v>
+        <v>221.6599870508316</v>
       </c>
       <c r="E28">
-        <v>-57.826</v>
+        <v>-55.77699999999999</v>
       </c>
       <c r="F28">
-        <v>53.27399999999999</v>
+        <v>55.323</v>
       </c>
       <c r="G28">
         <v>10.3</v>
@@ -3583,28 +3583,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M28">
-        <v>2.8927782</v>
+        <v>3.0040389</v>
       </c>
       <c r="N28">
-        <v>18.40314016734694</v>
+        <v>18.29187946734694</v>
       </c>
       <c r="O28">
-        <v>2.760471025102041</v>
+        <v>2.743781920102041</v>
       </c>
       <c r="P28">
-        <v>15.6426691422449</v>
+        <v>15.5480975472449</v>
       </c>
       <c r="Q28">
-        <v>19.1426691422449</v>
+        <v>19.0480975472449</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1436045226953325</v>
+        <v>0.1447895588918036</v>
       </c>
       <c r="T28">
-        <v>1.274720800964603</v>
+        <v>1.290165795203195</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.36175292227622</v>
+        <v>7.089095406636358</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1181582279910166</v>
+        <v>0.1180488091874871</v>
       </c>
       <c r="C29">
-        <v>176.6369870508316</v>
+        <v>174.9236849100242</v>
       </c>
       <c r="D29">
-        <v>221.6599870508316</v>
+        <v>221.9956849100242</v>
       </c>
       <c r="E29">
-        <v>-55.77699999999999</v>
+        <v>-53.72799999999999</v>
       </c>
       <c r="F29">
-        <v>55.323</v>
+        <v>57.372</v>
       </c>
       <c r="G29">
         <v>10.3</v>
@@ -3665,28 +3665,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M29">
-        <v>3.0040389</v>
+        <v>3.1152996</v>
       </c>
       <c r="N29">
-        <v>18.29187946734694</v>
+        <v>18.18061876734694</v>
       </c>
       <c r="O29">
-        <v>2.743781920102041</v>
+        <v>2.727092815102041</v>
       </c>
       <c r="P29">
-        <v>15.5480975472449</v>
+        <v>15.4535259522449</v>
       </c>
       <c r="Q29">
-        <v>19.0480975472449</v>
+        <v>18.9535259522449</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1447895588918036</v>
+        <v>0.1460075127603988</v>
       </c>
       <c r="T29">
-        <v>1.290165795203195</v>
+        <v>1.306039817059525</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.089095406636358</v>
+        <v>6.835913427827917</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1180488091874871</v>
+        <v>0.1179393903839577</v>
       </c>
       <c r="C30">
-        <v>174.9236849100242</v>
+        <v>173.2114011215458</v>
       </c>
       <c r="D30">
-        <v>221.9956849100242</v>
+        <v>222.3324011215458</v>
       </c>
       <c r="E30">
-        <v>-53.72799999999999</v>
+        <v>-51.67899999999999</v>
       </c>
       <c r="F30">
-        <v>57.372</v>
+        <v>59.421</v>
       </c>
       <c r="G30">
         <v>10.3</v>
@@ -3747,28 +3747,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M30">
-        <v>3.1152996</v>
+        <v>3.2265603</v>
       </c>
       <c r="N30">
-        <v>18.18061876734694</v>
+        <v>18.06935806734694</v>
       </c>
       <c r="O30">
-        <v>2.727092815102041</v>
+        <v>2.710403710102041</v>
       </c>
       <c r="P30">
-        <v>15.4535259522449</v>
+        <v>15.3589543572449</v>
       </c>
       <c r="Q30">
-        <v>18.9535259522449</v>
+        <v>18.8589543572449</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1460075127603988</v>
+        <v>0.1472597751886728</v>
       </c>
       <c r="T30">
-        <v>1.306039817059525</v>
+        <v>1.322360994461104</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.835913427827917</v>
+        <v>6.600192275144196</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1179393903839576</v>
+        <v>0.1178299715804282</v>
       </c>
       <c r="C31">
-        <v>173.2114011215459</v>
+        <v>171.5001403262517</v>
       </c>
       <c r="D31">
-        <v>222.3324011215458</v>
+        <v>222.6701403262516</v>
       </c>
       <c r="E31">
-        <v>-51.679</v>
+        <v>-49.63</v>
       </c>
       <c r="F31">
-        <v>59.42099999999999</v>
+        <v>61.46999999999999</v>
       </c>
       <c r="G31">
         <v>10.3</v>
@@ -3829,28 +3829,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M31">
-        <v>3.2265603</v>
+        <v>3.337820999999999</v>
       </c>
       <c r="N31">
-        <v>18.06935806734694</v>
+        <v>17.95809736734694</v>
       </c>
       <c r="O31">
-        <v>2.710403710102041</v>
+        <v>2.693714605102041</v>
       </c>
       <c r="P31">
-        <v>15.3589543572449</v>
+        <v>15.2643827622449</v>
       </c>
       <c r="Q31">
-        <v>18.8589543572449</v>
+        <v>18.7643827622449</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1472597751886728</v>
+        <v>0.1485478165434689</v>
       </c>
       <c r="T31">
-        <v>1.322360994461104</v>
+        <v>1.339148491217014</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.600192275144197</v>
+        <v>6.380185865972724</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1178299715804282</v>
+        <v>0.1177205527768987</v>
       </c>
       <c r="C32">
-        <v>171.5001403262517</v>
+        <v>169.7899071932391</v>
       </c>
       <c r="D32">
-        <v>222.6701403262516</v>
+        <v>223.0089071932391</v>
       </c>
       <c r="E32">
-        <v>-49.63</v>
+        <v>-47.581</v>
       </c>
       <c r="F32">
-        <v>61.46999999999999</v>
+        <v>63.51899999999999</v>
       </c>
       <c r="G32">
         <v>10.3</v>
@@ -3911,28 +3911,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M32">
-        <v>3.337820999999999</v>
+        <v>3.4490817</v>
       </c>
       <c r="N32">
-        <v>17.95809736734694</v>
+        <v>17.84683666734694</v>
       </c>
       <c r="O32">
-        <v>2.693714605102041</v>
+        <v>2.677025500102041</v>
       </c>
       <c r="P32">
-        <v>15.2643827622449</v>
+        <v>15.1698111672449</v>
       </c>
       <c r="Q32">
-        <v>18.7643827622449</v>
+        <v>18.6698111672449</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1485478165434689</v>
+        <v>0.149873192430288</v>
       </c>
       <c r="T32">
-        <v>1.339148491217014</v>
+        <v>1.356422582081791</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.380185865972724</v>
+        <v>6.17437341868328</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1177205527768987</v>
+        <v>0.1178831339733692</v>
       </c>
       <c r="C33">
-        <v>169.7899071932391</v>
+        <v>167.2379177565082</v>
       </c>
       <c r="D33">
-        <v>223.0089071932391</v>
+        <v>222.5059177565082</v>
       </c>
       <c r="E33">
-        <v>-47.581</v>
+        <v>-45.532</v>
       </c>
       <c r="F33">
-        <v>63.51899999999999</v>
+        <v>65.568</v>
       </c>
       <c r="G33">
         <v>10.3</v>
@@ -3993,45 +3993,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M33">
-        <v>3.4490817</v>
+        <v>3.6259104</v>
       </c>
       <c r="N33">
-        <v>17.84683666734694</v>
+        <v>17.67000796734694</v>
       </c>
       <c r="O33">
-        <v>2.677025500102041</v>
+        <v>2.650501195102041</v>
       </c>
       <c r="P33">
-        <v>15.1698111672449</v>
+        <v>15.0195067722449</v>
       </c>
       <c r="Q33">
-        <v>18.6698111672449</v>
+        <v>18.5195067722449</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.149873192430288</v>
+        <v>0.1512375499608371</v>
       </c>
       <c r="T33">
-        <v>1.356422582081791</v>
+        <v>1.37420473444259</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.15</v>
       </c>
       <c r="W33">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.17437341868328</v>
+        <v>5.873261062200252</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1178831339733692</v>
+        <v>0.1177822151698398</v>
       </c>
       <c r="C34">
-        <v>167.2379177565082</v>
+        <v>165.5008702428999</v>
       </c>
       <c r="D34">
-        <v>222.5059177565082</v>
+        <v>222.8178702428999</v>
       </c>
       <c r="E34">
-        <v>-45.532</v>
+        <v>-43.483</v>
       </c>
       <c r="F34">
-        <v>65.568</v>
+        <v>67.61699999999999</v>
       </c>
       <c r="G34">
         <v>10.3</v>
@@ -4075,28 +4075,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M34">
-        <v>3.6259104</v>
+        <v>3.739220099999999</v>
       </c>
       <c r="N34">
-        <v>17.67000796734694</v>
+        <v>17.55669826734694</v>
       </c>
       <c r="O34">
-        <v>2.650501195102041</v>
+        <v>2.633504740102041</v>
       </c>
       <c r="P34">
-        <v>15.0195067722449</v>
+        <v>14.9231935272449</v>
       </c>
       <c r="Q34">
-        <v>18.5195067722449</v>
+        <v>18.4231935272449</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1512375499608371</v>
+        <v>0.1526426345818504</v>
       </c>
       <c r="T34">
-        <v>1.37420473444259</v>
+        <v>1.392517697321622</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.873261062200252</v>
+        <v>5.69528345425479</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1177822151698398</v>
+        <v>0.1176812963663103</v>
       </c>
       <c r="C35">
-        <v>165.5008702428999</v>
+        <v>163.7646986698568</v>
       </c>
       <c r="D35">
-        <v>222.8178702428999</v>
+        <v>223.1306986698568</v>
       </c>
       <c r="E35">
-        <v>-43.483</v>
+        <v>-41.434</v>
       </c>
       <c r="F35">
-        <v>67.61699999999999</v>
+        <v>69.666</v>
       </c>
       <c r="G35">
         <v>10.3</v>
@@ -4157,28 +4157,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M35">
-        <v>3.739220099999999</v>
+        <v>3.8525298</v>
       </c>
       <c r="N35">
-        <v>17.55669826734694</v>
+        <v>17.44338856734694</v>
       </c>
       <c r="O35">
-        <v>2.633504740102041</v>
+        <v>2.616508285102041</v>
       </c>
       <c r="P35">
-        <v>14.9231935272449</v>
+        <v>14.8268802822449</v>
       </c>
       <c r="Q35">
-        <v>18.4231935272449</v>
+        <v>18.3268802822449</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1526426345818504</v>
+        <v>0.1540902975247126</v>
       </c>
       <c r="T35">
-        <v>1.392517697321622</v>
+        <v>1.411385598469717</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.69528345425479</v>
+        <v>5.527775117364943</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1176812963663103</v>
+        <v>0.1175803775627808</v>
       </c>
       <c r="C36">
-        <v>163.7646986698568</v>
+        <v>162.0294067319349</v>
       </c>
       <c r="D36">
-        <v>223.1306986698568</v>
+        <v>223.4444067319349</v>
       </c>
       <c r="E36">
-        <v>-41.434</v>
+        <v>-39.38499999999999</v>
       </c>
       <c r="F36">
-        <v>69.666</v>
+        <v>71.715</v>
       </c>
       <c r="G36">
         <v>10.3</v>
@@ -4239,28 +4239,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M36">
-        <v>3.8525298</v>
+        <v>3.9658395</v>
       </c>
       <c r="N36">
-        <v>17.44338856734694</v>
+        <v>17.33007886734694</v>
       </c>
       <c r="O36">
-        <v>2.616508285102041</v>
+        <v>2.599511830102041</v>
       </c>
       <c r="P36">
-        <v>14.8268802822449</v>
+        <v>14.7305670372449</v>
       </c>
       <c r="Q36">
-        <v>18.3268802822449</v>
+        <v>18.2305670372449</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1540902975247126</v>
+        <v>0.1555825039427398</v>
       </c>
       <c r="T36">
-        <v>1.411385598469717</v>
+        <v>1.430834050422367</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.527775117364943</v>
+        <v>5.36983868544023</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1175803775627808</v>
+        <v>0.1174794587592514</v>
       </c>
       <c r="C37">
-        <v>162.0294067319349</v>
+        <v>160.2949981444968</v>
       </c>
       <c r="D37">
-        <v>223.4444067319349</v>
+        <v>223.7589981444968</v>
       </c>
       <c r="E37">
-        <v>-39.38499999999999</v>
+        <v>-37.336</v>
       </c>
       <c r="F37">
-        <v>71.715</v>
+        <v>73.764</v>
       </c>
       <c r="G37">
         <v>10.3</v>
@@ -4321,28 +4321,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M37">
-        <v>3.9658395</v>
+        <v>4.0791492</v>
       </c>
       <c r="N37">
-        <v>17.33007886734694</v>
+        <v>17.21676916734694</v>
       </c>
       <c r="O37">
-        <v>2.599511830102041</v>
+        <v>2.582515375102041</v>
       </c>
       <c r="P37">
-        <v>14.7305670372449</v>
+        <v>14.6342537922449</v>
       </c>
       <c r="Q37">
-        <v>18.2305670372449</v>
+        <v>18.1342537922449</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1555825039427398</v>
+        <v>0.1571213418113303</v>
       </c>
       <c r="T37">
-        <v>1.430834050422367</v>
+        <v>1.450890266498538</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.36983868544023</v>
+        <v>5.220676499733557</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1174794587592514</v>
+        <v>0.1173785399557219</v>
       </c>
       <c r="C38">
-        <v>160.2949981444968</v>
+        <v>158.561476643858</v>
       </c>
       <c r="D38">
-        <v>223.7589981444968</v>
+        <v>224.0744766438579</v>
       </c>
       <c r="E38">
-        <v>-37.336</v>
+        <v>-35.28700000000001</v>
       </c>
       <c r="F38">
-        <v>73.764</v>
+        <v>75.81299999999999</v>
       </c>
       <c r="G38">
         <v>10.3</v>
@@ -4403,28 +4403,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M38">
-        <v>4.0791492</v>
+        <v>4.192458899999999</v>
       </c>
       <c r="N38">
-        <v>17.21676916734694</v>
+        <v>17.10345946734694</v>
       </c>
       <c r="O38">
-        <v>2.582515375102041</v>
+        <v>2.565518920102041</v>
       </c>
       <c r="P38">
-        <v>14.6342537922449</v>
+        <v>14.5379405472449</v>
       </c>
       <c r="Q38">
-        <v>18.1342537922449</v>
+        <v>18.0379405472449</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1571213418113303</v>
+        <v>0.1587090316757491</v>
       </c>
       <c r="T38">
-        <v>1.450890266498538</v>
+        <v>1.471583187846969</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.220676499733557</v>
+        <v>5.079577134875894</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1173785399557219</v>
+        <v>0.1172776211521925</v>
       </c>
       <c r="C39">
-        <v>158.561476643858</v>
+        <v>156.8288459874352</v>
       </c>
       <c r="D39">
-        <v>224.0744766438579</v>
+        <v>224.3908459874352</v>
       </c>
       <c r="E39">
-        <v>-35.28700000000001</v>
+        <v>-33.238</v>
       </c>
       <c r="F39">
-        <v>75.81299999999999</v>
+        <v>77.86199999999999</v>
       </c>
       <c r="G39">
         <v>10.3</v>
@@ -4485,28 +4485,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M39">
-        <v>4.192458899999999</v>
+        <v>4.3057686</v>
       </c>
       <c r="N39">
-        <v>17.10345946734694</v>
+        <v>16.99014976734694</v>
       </c>
       <c r="O39">
-        <v>2.565518920102041</v>
+        <v>2.548522465102041</v>
       </c>
       <c r="P39">
-        <v>14.5379405472449</v>
+        <v>14.4416273022449</v>
       </c>
       <c r="Q39">
-        <v>18.0379405472449</v>
+        <v>17.9416273022449</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1587090316757491</v>
+        <v>0.1603479373422459</v>
       </c>
       <c r="T39">
-        <v>1.471583187846969</v>
+        <v>1.492943622787284</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.079577134875894</v>
+        <v>4.945904052379159</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1172776211521925</v>
+        <v>0.117176702348663</v>
       </c>
       <c r="C40">
-        <v>156.8288459874352</v>
+        <v>155.0971099538959</v>
       </c>
       <c r="D40">
-        <v>224.3908459874352</v>
+        <v>224.7081099538959</v>
       </c>
       <c r="E40">
-        <v>-33.238</v>
+        <v>-31.18900000000001</v>
       </c>
       <c r="F40">
-        <v>77.86199999999999</v>
+        <v>79.91099999999999</v>
       </c>
       <c r="G40">
         <v>10.3</v>
@@ -4567,28 +4567,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M40">
-        <v>4.3057686</v>
+        <v>4.4190783</v>
       </c>
       <c r="N40">
-        <v>16.99014976734694</v>
+        <v>16.87684006734694</v>
       </c>
       <c r="O40">
-        <v>2.548522465102041</v>
+        <v>2.531526010102041</v>
       </c>
       <c r="P40">
-        <v>14.4416273022449</v>
+        <v>14.3453140572449</v>
       </c>
       <c r="Q40">
-        <v>17.9416273022449</v>
+        <v>17.8453140572449</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1603479373422459</v>
+        <v>0.162040577620759</v>
       </c>
       <c r="T40">
-        <v>1.492943622787284</v>
+        <v>1.51500439985679</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.945904052379159</v>
+        <v>4.819085999754053</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.117176702348663</v>
+        <v>0.1170757835451335</v>
       </c>
       <c r="C41">
-        <v>155.0971099538959</v>
+        <v>153.3662723433077</v>
       </c>
       <c r="D41">
-        <v>224.7081099538959</v>
+        <v>225.0262723433077</v>
       </c>
       <c r="E41">
-        <v>-31.18900000000001</v>
+        <v>-29.14</v>
       </c>
       <c r="F41">
-        <v>79.91099999999999</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="G41">
         <v>10.3</v>
@@ -4649,28 +4649,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M41">
-        <v>4.4190783</v>
+        <v>4.532388</v>
       </c>
       <c r="N41">
-        <v>16.87684006734694</v>
+        <v>16.76353036734694</v>
       </c>
       <c r="O41">
-        <v>2.531526010102041</v>
+        <v>2.514529555102041</v>
       </c>
       <c r="P41">
-        <v>14.3453140572449</v>
+        <v>14.2490008122449</v>
       </c>
       <c r="Q41">
-        <v>17.8453140572449</v>
+        <v>17.7490008122449</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.162040577620759</v>
+        <v>0.1637896392418892</v>
       </c>
       <c r="T41">
-        <v>1.51500439985679</v>
+        <v>1.537800536161946</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.819085999754053</v>
+        <v>4.698608849760201</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1170757835451335</v>
+        <v>0.116974864741604</v>
       </c>
       <c r="C42">
-        <v>153.3662723433077</v>
+        <v>151.6363369772909</v>
       </c>
       <c r="D42">
-        <v>225.0262723433077</v>
+        <v>225.3453369772909</v>
       </c>
       <c r="E42">
-        <v>-29.14</v>
+        <v>-27.09099999999999</v>
       </c>
       <c r="F42">
-        <v>81.95999999999999</v>
+        <v>84.009</v>
       </c>
       <c r="G42">
         <v>10.3</v>
@@ -4731,28 +4731,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M42">
-        <v>4.532388</v>
+        <v>4.6456977</v>
       </c>
       <c r="N42">
-        <v>16.76353036734694</v>
+        <v>16.65022066734694</v>
       </c>
       <c r="O42">
-        <v>2.514529555102041</v>
+        <v>2.497533100102041</v>
       </c>
       <c r="P42">
-        <v>14.2490008122449</v>
+        <v>14.1526875672449</v>
       </c>
       <c r="Q42">
-        <v>17.7490008122449</v>
+        <v>17.6526875672449</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1637896392418892</v>
+        <v>0.1655979910874645</v>
       </c>
       <c r="T42">
-        <v>1.537800536161946</v>
+        <v>1.561369422850328</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.698608849760201</v>
+        <v>4.584008633912392</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.116974864741604</v>
+        <v>0.1177664459380746</v>
       </c>
       <c r="C43">
-        <v>151.6363369772909</v>
+        <v>147.1086939216504</v>
       </c>
       <c r="D43">
-        <v>225.3453369772909</v>
+        <v>222.8666939216504</v>
       </c>
       <c r="E43">
-        <v>-27.09099999999999</v>
+        <v>-25.042</v>
       </c>
       <c r="F43">
-        <v>84.009</v>
+        <v>86.05799999999999</v>
       </c>
       <c r="G43">
         <v>10.3</v>
@@ -4813,45 +4813,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M43">
-        <v>4.6456977</v>
+        <v>4.9741524</v>
       </c>
       <c r="N43">
-        <v>16.65022066734694</v>
+        <v>16.32176596734694</v>
       </c>
       <c r="O43">
-        <v>2.497533100102041</v>
+        <v>2.44826489510204</v>
       </c>
       <c r="P43">
-        <v>14.1526875672449</v>
+        <v>13.8735010722449</v>
       </c>
       <c r="Q43">
-        <v>17.6526875672449</v>
+        <v>17.3735010722449</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1655979910874645</v>
+        <v>0.167468699893232</v>
       </c>
       <c r="T43">
-        <v>1.561369422850328</v>
+        <v>1.585751029769344</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.15</v>
       </c>
       <c r="W43">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.584008633912392</v>
+        <v>4.281316022272847</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1177664459380746</v>
+        <v>0.1176867771345451</v>
       </c>
       <c r="C44">
-        <v>147.1086939216503</v>
+        <v>145.3066868118459</v>
       </c>
       <c r="D44">
-        <v>222.8666939216503</v>
+        <v>223.1136868118459</v>
       </c>
       <c r="E44">
-        <v>-25.042</v>
+        <v>-22.99300000000001</v>
       </c>
       <c r="F44">
-        <v>86.05799999999999</v>
+        <v>88.10699999999999</v>
       </c>
       <c r="G44">
         <v>10.3</v>
@@ -4895,28 +4895,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M44">
-        <v>4.9741524</v>
+        <v>5.092584599999999</v>
       </c>
       <c r="N44">
-        <v>16.32176596734694</v>
+        <v>16.20333376734694</v>
       </c>
       <c r="O44">
-        <v>2.44826489510204</v>
+        <v>2.430500065102041</v>
       </c>
       <c r="P44">
-        <v>13.8735010722449</v>
+        <v>13.7728337022449</v>
       </c>
       <c r="Q44">
-        <v>17.3735010722449</v>
+        <v>17.2728337022449</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.167468699893232</v>
+        <v>0.1694050476044651</v>
       </c>
       <c r="T44">
-        <v>1.585751029769343</v>
+        <v>1.610988131667974</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.281316022272847</v>
+        <v>4.181750533382782</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1176867771345451</v>
+        <v>0.1176071083310156</v>
       </c>
       <c r="C45">
-        <v>145.3066868118459</v>
+        <v>143.5052277711254</v>
       </c>
       <c r="D45">
-        <v>223.1136868118459</v>
+        <v>223.3612277711254</v>
       </c>
       <c r="E45">
-        <v>-22.99300000000001</v>
+        <v>-20.944</v>
       </c>
       <c r="F45">
-        <v>88.10699999999999</v>
+        <v>90.15599999999999</v>
       </c>
       <c r="G45">
         <v>10.3</v>
@@ -4977,28 +4977,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M45">
-        <v>5.092584599999999</v>
+        <v>5.2110168</v>
       </c>
       <c r="N45">
-        <v>16.20333376734694</v>
+        <v>16.08490156734694</v>
       </c>
       <c r="O45">
-        <v>2.430500065102041</v>
+        <v>2.412735235102041</v>
       </c>
       <c r="P45">
-        <v>13.7728337022449</v>
+        <v>13.6721663322449</v>
       </c>
       <c r="Q45">
-        <v>17.2728337022449</v>
+        <v>17.1721663322449</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1694050476044651</v>
+        <v>0.1714105505910994</v>
       </c>
       <c r="T45">
-        <v>1.610988131667974</v>
+        <v>1.637126558634412</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.181750533382782</v>
+        <v>4.086710748533173</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1176071083310156</v>
+        <v>0.1188661895274862</v>
       </c>
       <c r="C46">
-        <v>143.5052277711254</v>
+        <v>137.607252975452</v>
       </c>
       <c r="D46">
-        <v>223.3612277711254</v>
+        <v>219.5122529754519</v>
       </c>
       <c r="E46">
-        <v>-20.944</v>
+        <v>-18.895</v>
       </c>
       <c r="F46">
-        <v>90.15599999999999</v>
+        <v>92.205</v>
       </c>
       <c r="G46">
         <v>10.3</v>
@@ -5059,45 +5059,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M46">
-        <v>5.2110168</v>
+        <v>5.6521665</v>
       </c>
       <c r="N46">
-        <v>16.08490156734694</v>
+        <v>15.64375186734694</v>
       </c>
       <c r="O46">
-        <v>2.412735235102041</v>
+        <v>2.346562780102041</v>
       </c>
       <c r="P46">
-        <v>13.6721663322449</v>
+        <v>13.2971890872449</v>
       </c>
       <c r="Q46">
-        <v>17.1721663322449</v>
+        <v>16.7971890872449</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1714105505910994</v>
+        <v>0.1734889809590658</v>
       </c>
       <c r="T46">
-        <v>1.637126558634412</v>
+        <v>1.664215473854176</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.15</v>
       </c>
       <c r="W46">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.086710748533173</v>
+        <v>3.767744344995311</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1188661895274862</v>
+        <v>0.1188162707239567</v>
       </c>
       <c r="C47">
-        <v>137.607252975452</v>
+        <v>135.7083262251529</v>
       </c>
       <c r="D47">
-        <v>219.5122529754519</v>
+        <v>219.6623262251529</v>
       </c>
       <c r="E47">
-        <v>-18.895</v>
+        <v>-16.846</v>
       </c>
       <c r="F47">
-        <v>92.205</v>
+        <v>94.25399999999999</v>
       </c>
       <c r="G47">
         <v>10.3</v>
@@ -5141,28 +5141,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M47">
-        <v>5.6521665</v>
+        <v>5.777770199999999</v>
       </c>
       <c r="N47">
-        <v>15.64375186734694</v>
+        <v>15.51814816734694</v>
       </c>
       <c r="O47">
-        <v>2.346562780102041</v>
+        <v>2.327722225102041</v>
       </c>
       <c r="P47">
-        <v>13.2971890872449</v>
+        <v>13.1904259422449</v>
       </c>
       <c r="Q47">
-        <v>16.7971890872449</v>
+        <v>16.6904259422449</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1734889809590658</v>
+        <v>0.1756443902295494</v>
       </c>
       <c r="T47">
-        <v>1.664215473854176</v>
+        <v>1.692307682230227</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.767744344995311</v>
+        <v>3.685836859234544</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1188162707239567</v>
+        <v>0.1187663519204272</v>
       </c>
       <c r="C48">
-        <v>135.7083262251529</v>
+        <v>133.8096048154492</v>
       </c>
       <c r="D48">
-        <v>219.6623262251529</v>
+        <v>219.8126048154492</v>
       </c>
       <c r="E48">
-        <v>-16.846</v>
+        <v>-14.797</v>
       </c>
       <c r="F48">
-        <v>94.25399999999999</v>
+        <v>96.303</v>
       </c>
       <c r="G48">
         <v>10.3</v>
@@ -5223,28 +5223,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M48">
-        <v>5.777770199999999</v>
+        <v>5.9033739</v>
       </c>
       <c r="N48">
-        <v>15.51814816734694</v>
+        <v>15.39254446734694</v>
       </c>
       <c r="O48">
-        <v>2.327722225102041</v>
+        <v>2.308881670102041</v>
       </c>
       <c r="P48">
-        <v>13.1904259422449</v>
+        <v>13.0836627972449</v>
       </c>
       <c r="Q48">
-        <v>16.6904259422449</v>
+        <v>16.5836627972449</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1756443902295494</v>
+        <v>0.1778811356989193</v>
       </c>
       <c r="T48">
-        <v>1.692307682230227</v>
+        <v>1.721459973941223</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.685836859234544</v>
+        <v>3.607414798399766</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1187663519204272</v>
+        <v>0.1187164331168978</v>
       </c>
       <c r="C49">
-        <v>133.8096048154492</v>
+        <v>131.9110891680709</v>
       </c>
       <c r="D49">
-        <v>219.8126048154492</v>
+        <v>219.9630891680709</v>
       </c>
       <c r="E49">
-        <v>-14.797</v>
+        <v>-12.74799999999999</v>
       </c>
       <c r="F49">
-        <v>96.303</v>
+        <v>98.352</v>
       </c>
       <c r="G49">
         <v>10.3</v>
@@ -5305,28 +5305,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M49">
-        <v>5.9033739</v>
+        <v>6.0289776</v>
       </c>
       <c r="N49">
-        <v>15.39254446734694</v>
+        <v>15.26694076734694</v>
       </c>
       <c r="O49">
-        <v>2.308881670102041</v>
+        <v>2.290041115102041</v>
       </c>
       <c r="P49">
-        <v>13.0836627972449</v>
+        <v>12.9768996522449</v>
       </c>
       <c r="Q49">
-        <v>16.5836627972449</v>
+        <v>16.4768996522449</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1778811356989193</v>
+        <v>0.180203909840188</v>
       </c>
       <c r="T49">
-        <v>1.721459973941223</v>
+        <v>1.751733507641104</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.607414798399766</v>
+        <v>3.532260323433104</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1187164331168978</v>
+        <v>0.1198327143133683</v>
       </c>
       <c r="C50">
-        <v>131.9110891680709</v>
+        <v>126.5454383788462</v>
       </c>
       <c r="D50">
-        <v>219.9630891680709</v>
+        <v>216.6464383788461</v>
       </c>
       <c r="E50">
-        <v>-12.748</v>
+        <v>-10.69900000000001</v>
       </c>
       <c r="F50">
-        <v>98.35199999999999</v>
+        <v>100.401</v>
       </c>
       <c r="G50">
         <v>10.3</v>
@@ -5387,45 +5387,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M50">
-        <v>6.028977599999999</v>
+        <v>6.4357041</v>
       </c>
       <c r="N50">
-        <v>15.26694076734694</v>
+        <v>14.86021426734694</v>
       </c>
       <c r="O50">
-        <v>2.290041115102041</v>
+        <v>2.229032140102041</v>
       </c>
       <c r="P50">
-        <v>12.9768996522449</v>
+        <v>12.6311821272449</v>
       </c>
       <c r="Q50">
-        <v>16.4768996522449</v>
+        <v>16.1311821272449</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.180203909840188</v>
+        <v>0.1826177731634672</v>
       </c>
       <c r="T50">
-        <v>1.751733507641104</v>
+        <v>1.78319423874098</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.15</v>
       </c>
       <c r="W50">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.532260323433104</v>
+        <v>3.309026959046632</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1198327143133683</v>
+        <v>0.1198065955098388</v>
       </c>
       <c r="C51">
-        <v>126.5454383788462</v>
+        <v>124.5728983986645</v>
       </c>
       <c r="D51">
-        <v>216.6464383788461</v>
+        <v>216.7228983986645</v>
       </c>
       <c r="E51">
-        <v>-10.69900000000001</v>
+        <v>-8.650000000000006</v>
       </c>
       <c r="F51">
-        <v>100.401</v>
+        <v>102.45</v>
       </c>
       <c r="G51">
         <v>10.3</v>
@@ -5469,28 +5469,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M51">
-        <v>6.4357041</v>
+        <v>6.567044999999999</v>
       </c>
       <c r="N51">
-        <v>14.86021426734694</v>
+        <v>14.72887336734694</v>
       </c>
       <c r="O51">
-        <v>2.229032140102041</v>
+        <v>2.209331005102041</v>
       </c>
       <c r="P51">
-        <v>12.6311821272449</v>
+        <v>12.5195423622449</v>
       </c>
       <c r="Q51">
-        <v>16.1311821272449</v>
+        <v>16.0195423622449</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1826177731634672</v>
+        <v>0.1851281910196776</v>
       </c>
       <c r="T51">
-        <v>1.78319423874098</v>
+        <v>1.815913399084851</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.309026959046632</v>
+        <v>3.242846419865699</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1198065955098388</v>
+        <v>0.1197804767063094</v>
       </c>
       <c r="C52">
-        <v>124.5728983986645</v>
+        <v>122.6004124068951</v>
       </c>
       <c r="D52">
-        <v>216.7228983986645</v>
+        <v>216.7994124068951</v>
       </c>
       <c r="E52">
-        <v>-8.650000000000006</v>
+        <v>-6.600999999999999</v>
       </c>
       <c r="F52">
-        <v>102.45</v>
+        <v>104.499</v>
       </c>
       <c r="G52">
         <v>10.3</v>
@@ -5551,28 +5551,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M52">
-        <v>6.567044999999999</v>
+        <v>6.6983859</v>
       </c>
       <c r="N52">
-        <v>14.72887336734694</v>
+        <v>14.59753246734694</v>
       </c>
       <c r="O52">
-        <v>2.209331005102041</v>
+        <v>2.189629870102041</v>
       </c>
       <c r="P52">
-        <v>12.5195423622449</v>
+        <v>12.4079025972449</v>
       </c>
       <c r="Q52">
-        <v>16.0195423622449</v>
+        <v>15.9079025972449</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1851281910196776</v>
+        <v>0.1877410749108354</v>
       </c>
       <c r="T52">
-        <v>1.815913399084851</v>
+        <v>1.849968035361125</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.242846419865699</v>
+        <v>3.179261195946764</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1197804767063094</v>
+        <v>0.1197543579027799</v>
       </c>
       <c r="C53">
-        <v>122.6004124068951</v>
+        <v>120.6279804607399</v>
       </c>
       <c r="D53">
-        <v>216.7994124068951</v>
+        <v>216.8759804607399</v>
       </c>
       <c r="E53">
-        <v>-6.600999999999999</v>
+        <v>-4.552000000000007</v>
       </c>
       <c r="F53">
-        <v>104.499</v>
+        <v>106.548</v>
       </c>
       <c r="G53">
         <v>10.3</v>
@@ -5633,28 +5633,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M53">
-        <v>6.6983859</v>
+        <v>6.8297268</v>
       </c>
       <c r="N53">
-        <v>14.59753246734694</v>
+        <v>14.46619156734694</v>
       </c>
       <c r="O53">
-        <v>2.189629870102041</v>
+        <v>2.169928735102041</v>
       </c>
       <c r="P53">
-        <v>12.4079025972449</v>
+        <v>12.2962628322449</v>
       </c>
       <c r="Q53">
-        <v>15.9079025972449</v>
+        <v>15.7962628322449</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1877410749108354</v>
+        <v>0.1904628289641248</v>
       </c>
       <c r="T53">
-        <v>1.849968035361125</v>
+        <v>1.885441614815577</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.179261195946764</v>
+        <v>3.118121557563172</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1197543579027799</v>
+        <v>0.1197282390992504</v>
       </c>
       <c r="C54">
-        <v>120.6279804607399</v>
+        <v>118.6556026174818</v>
       </c>
       <c r="D54">
-        <v>216.8759804607399</v>
+        <v>216.9526026174818</v>
       </c>
       <c r="E54">
-        <v>-4.552000000000007</v>
+        <v>-2.503</v>
       </c>
       <c r="F54">
-        <v>106.548</v>
+        <v>108.597</v>
       </c>
       <c r="G54">
         <v>10.3</v>
@@ -5715,28 +5715,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M54">
-        <v>6.8297268</v>
+        <v>6.9610677</v>
       </c>
       <c r="N54">
-        <v>14.46619156734694</v>
+        <v>14.33485066734694</v>
       </c>
       <c r="O54">
-        <v>2.169928735102041</v>
+        <v>2.150227600102041</v>
       </c>
       <c r="P54">
-        <v>12.2962628322449</v>
+        <v>12.1846230672449</v>
       </c>
       <c r="Q54">
-        <v>15.7962628322449</v>
+        <v>15.6846230672449</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1904628289641248</v>
+        <v>0.1933004023388307</v>
       </c>
       <c r="T54">
-        <v>1.885441614815577</v>
+        <v>1.922424708289368</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.118121557563172</v>
+        <v>3.059289075344999</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1197282390992504</v>
+        <v>0.1197021202957209</v>
       </c>
       <c r="C55">
-        <v>118.6556026174818</v>
+        <v>116.6832789344847</v>
       </c>
       <c r="D55">
-        <v>216.9526026174818</v>
+        <v>217.0292789344847</v>
       </c>
       <c r="E55">
-        <v>-2.503</v>
+        <v>-0.4539999999999935</v>
       </c>
       <c r="F55">
-        <v>108.597</v>
+        <v>110.646</v>
       </c>
       <c r="G55">
         <v>10.3</v>
@@ -5797,28 +5797,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M55">
-        <v>6.9610677</v>
+        <v>7.092408600000001</v>
       </c>
       <c r="N55">
-        <v>14.33485066734694</v>
+        <v>14.20350976734694</v>
       </c>
       <c r="O55">
-        <v>2.150227600102041</v>
+        <v>2.130526465102041</v>
       </c>
       <c r="P55">
-        <v>12.1846230672449</v>
+        <v>12.0729833022449</v>
       </c>
       <c r="Q55">
-        <v>15.6846230672449</v>
+        <v>15.5729833022449</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1933004023388307</v>
+        <v>0.1962613484689586</v>
       </c>
       <c r="T55">
-        <v>1.922424708289368</v>
+        <v>1.961015762348976</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.059289075344999</v>
+        <v>3.002635573949721</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1197021202957209</v>
+        <v>0.1233225014921915</v>
       </c>
       <c r="C56">
-        <v>116.6832789344847</v>
+        <v>104.4987865882126</v>
       </c>
       <c r="D56">
-        <v>217.0292789344847</v>
+        <v>206.8937865882125</v>
       </c>
       <c r="E56">
-        <v>-0.4539999999999935</v>
+        <v>1.594999999999999</v>
       </c>
       <c r="F56">
-        <v>110.646</v>
+        <v>112.695</v>
       </c>
       <c r="G56">
         <v>10.3</v>
@@ -5879,45 +5879,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M56">
-        <v>7.092408600000001</v>
+        <v>8.1027705</v>
       </c>
       <c r="N56">
-        <v>14.20350976734694</v>
+        <v>13.19314786734694</v>
       </c>
       <c r="O56">
-        <v>2.130526465102041</v>
+        <v>1.978972180102041</v>
       </c>
       <c r="P56">
-        <v>12.0729833022449</v>
+        <v>11.2141756872449</v>
       </c>
       <c r="Q56">
-        <v>15.5729833022449</v>
+        <v>14.7141756872449</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1962613484689586</v>
+        <v>0.19935389220487</v>
       </c>
       <c r="T56">
-        <v>1.961015762348976</v>
+        <v>2.001321974366788</v>
       </c>
       <c r="U56">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V56">
         <v>0.15</v>
       </c>
       <c r="W56">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.002635573949721</v>
+        <v>2.628226773465562</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1233225014921915</v>
+        <v>0.123362682688662</v>
       </c>
       <c r="C57">
-        <v>104.4987865882126</v>
+        <v>102.3426056656445</v>
       </c>
       <c r="D57">
-        <v>206.8937865882125</v>
+        <v>206.7866056656445</v>
       </c>
       <c r="E57">
-        <v>1.594999999999999</v>
+        <v>3.644000000000005</v>
       </c>
       <c r="F57">
-        <v>112.695</v>
+        <v>114.744</v>
       </c>
       <c r="G57">
         <v>10.3</v>
@@ -5961,28 +5961,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M57">
-        <v>8.1027705</v>
+        <v>8.250093600000001</v>
       </c>
       <c r="N57">
-        <v>13.19314786734694</v>
+        <v>13.04582476734694</v>
       </c>
       <c r="O57">
-        <v>1.978972180102041</v>
+        <v>1.956873715102041</v>
       </c>
       <c r="P57">
-        <v>11.2141756872449</v>
+        <v>11.0889510522449</v>
       </c>
       <c r="Q57">
-        <v>14.7141756872449</v>
+        <v>14.5889510522449</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.19935389220487</v>
+        <v>0.2025870061105955</v>
       </c>
       <c r="T57">
-        <v>2.001321974366788</v>
+        <v>2.043460286930865</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.628226773465562</v>
+        <v>2.58129415251082</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.123362682688662</v>
+        <v>0.1234028638851326</v>
       </c>
       <c r="C58">
-        <v>102.3426056656445</v>
+        <v>100.1865357353126</v>
       </c>
       <c r="D58">
-        <v>206.7866056656445</v>
+        <v>206.6795357353126</v>
       </c>
       <c r="E58">
-        <v>3.644000000000005</v>
+        <v>5.693000000000012</v>
       </c>
       <c r="F58">
-        <v>114.744</v>
+        <v>116.793</v>
       </c>
       <c r="G58">
         <v>10.3</v>
@@ -6043,28 +6043,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M58">
-        <v>8.250093600000001</v>
+        <v>8.397416700000001</v>
       </c>
       <c r="N58">
-        <v>13.04582476734694</v>
+        <v>12.89850166734694</v>
       </c>
       <c r="O58">
-        <v>1.956873715102041</v>
+        <v>1.934775250102041</v>
       </c>
       <c r="P58">
-        <v>11.0889510522449</v>
+        <v>10.9637264172449</v>
       </c>
       <c r="Q58">
-        <v>14.5889510522449</v>
+        <v>14.4637264172449</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2025870061105955</v>
+        <v>0.205970497407285</v>
       </c>
       <c r="T58">
-        <v>2.043460286930865</v>
+        <v>2.08755852100955</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.58129415251082</v>
+        <v>2.536008290186068</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1234028638851326</v>
+        <v>0.1253657450816031</v>
       </c>
       <c r="C59">
-        <v>100.1865357353126</v>
+        <v>93.03876648512808</v>
       </c>
       <c r="D59">
-        <v>206.6795357353126</v>
+        <v>201.5807664851281</v>
       </c>
       <c r="E59">
-        <v>5.693000000000012</v>
+        <v>7.742000000000004</v>
       </c>
       <c r="F59">
-        <v>116.793</v>
+        <v>118.842</v>
       </c>
       <c r="G59">
         <v>10.3</v>
@@ -6125,45 +6125,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M59">
-        <v>8.397416700000001</v>
+        <v>9.008223600000001</v>
       </c>
       <c r="N59">
-        <v>12.89850166734694</v>
+        <v>12.28769476734694</v>
       </c>
       <c r="O59">
-        <v>1.934775250102041</v>
+        <v>1.843154215102041</v>
       </c>
       <c r="P59">
-        <v>10.9637264172449</v>
+        <v>10.4445405522449</v>
       </c>
       <c r="Q59">
-        <v>14.4637264172449</v>
+        <v>13.9445405522449</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.205970497407285</v>
+        <v>0.2095151073371502</v>
       </c>
       <c r="T59">
-        <v>2.08755852100955</v>
+        <v>2.133756670996743</v>
       </c>
       <c r="U59">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.15</v>
       </c>
       <c r="W59">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.536008290186068</v>
+        <v>2.364053037864972</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1253657450816031</v>
+        <v>0.1254390762780736</v>
       </c>
       <c r="C60">
-        <v>93.03876648512809</v>
+        <v>90.8041520922617</v>
       </c>
       <c r="D60">
-        <v>201.5807664851281</v>
+        <v>201.3951520922617</v>
       </c>
       <c r="E60">
-        <v>7.74199999999999</v>
+        <v>9.790999999999983</v>
       </c>
       <c r="F60">
-        <v>118.842</v>
+        <v>120.891</v>
       </c>
       <c r="G60">
         <v>10.3</v>
@@ -6207,28 +6207,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M60">
-        <v>9.008223599999999</v>
+        <v>9.163537799999999</v>
       </c>
       <c r="N60">
-        <v>12.28769476734694</v>
+        <v>12.13238056734694</v>
       </c>
       <c r="O60">
-        <v>1.843154215102041</v>
+        <v>1.819857085102041</v>
       </c>
       <c r="P60">
-        <v>10.4445405522449</v>
+        <v>10.3125234822449</v>
       </c>
       <c r="Q60">
-        <v>13.9445405522449</v>
+        <v>13.8125234822449</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2095151073371502</v>
+        <v>0.2132326250684722</v>
       </c>
       <c r="T60">
-        <v>2.133756670996743</v>
+        <v>2.182208389275994</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.364053037864973</v>
+        <v>2.32398434230794</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1254390762780736</v>
+        <v>0.1255124074745441</v>
       </c>
       <c r="C61">
-        <v>90.8041520922617</v>
+        <v>88.56987921023257</v>
       </c>
       <c r="D61">
-        <v>201.3951520922617</v>
+        <v>201.2098792102325</v>
       </c>
       <c r="E61">
-        <v>9.790999999999983</v>
+        <v>11.83999999999999</v>
       </c>
       <c r="F61">
-        <v>120.891</v>
+        <v>122.94</v>
       </c>
       <c r="G61">
         <v>10.3</v>
@@ -6289,28 +6289,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M61">
-        <v>9.163537799999999</v>
+        <v>9.318852</v>
       </c>
       <c r="N61">
-        <v>12.13238056734694</v>
+        <v>11.97706636734694</v>
       </c>
       <c r="O61">
-        <v>1.819857085102041</v>
+        <v>1.796559955102041</v>
       </c>
       <c r="P61">
-        <v>10.3125234822449</v>
+        <v>10.1805064122449</v>
       </c>
       <c r="Q61">
-        <v>13.8125234822449</v>
+        <v>13.6805064122449</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2132326250684722</v>
+        <v>0.2171360186863603</v>
       </c>
       <c r="T61">
-        <v>2.182208389275994</v>
+        <v>2.233082693469208</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.32398434230794</v>
+        <v>2.28525126993614</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1255124074745441</v>
+        <v>0.1255857386710147</v>
       </c>
       <c r="C62">
-        <v>88.56987921023257</v>
+        <v>86.33594689739131</v>
       </c>
       <c r="D62">
-        <v>201.2098792102325</v>
+        <v>201.0249468973913</v>
       </c>
       <c r="E62">
-        <v>11.83999999999999</v>
+        <v>13.889</v>
       </c>
       <c r="F62">
-        <v>122.94</v>
+        <v>124.989</v>
       </c>
       <c r="G62">
         <v>10.3</v>
@@ -6371,28 +6371,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M62">
-        <v>9.318852</v>
+        <v>9.474166200000001</v>
       </c>
       <c r="N62">
-        <v>11.97706636734694</v>
+        <v>11.82175216734694</v>
       </c>
       <c r="O62">
-        <v>1.796559955102041</v>
+        <v>1.773262825102041</v>
       </c>
       <c r="P62">
-        <v>10.1805064122449</v>
+        <v>10.0484893422449</v>
       </c>
       <c r="Q62">
-        <v>13.6805064122449</v>
+        <v>13.5484893422449</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2171360186863603</v>
+        <v>0.221239586335935</v>
       </c>
       <c r="T62">
-        <v>2.233082693469208</v>
+        <v>2.286565936338998</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.28525126993614</v>
+        <v>2.247788134363416</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1255857386710147</v>
+        <v>0.1256590698674852</v>
       </c>
       <c r="C63">
-        <v>86.33594689739131</v>
+        <v>84.10235421554719</v>
       </c>
       <c r="D63">
-        <v>201.0249468973913</v>
+        <v>200.8403542155472</v>
       </c>
       <c r="E63">
-        <v>13.889</v>
+        <v>15.93799999999999</v>
       </c>
       <c r="F63">
-        <v>124.989</v>
+        <v>127.038</v>
       </c>
       <c r="G63">
         <v>10.3</v>
@@ -6453,28 +6453,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M63">
-        <v>9.474166200000001</v>
+        <v>9.6294804</v>
       </c>
       <c r="N63">
-        <v>11.82175216734694</v>
+        <v>11.66643796734694</v>
       </c>
       <c r="O63">
-        <v>1.773262825102041</v>
+        <v>1.749965695102041</v>
       </c>
       <c r="P63">
-        <v>10.0484893422449</v>
+        <v>9.916472272244897</v>
       </c>
       <c r="Q63">
-        <v>13.5484893422449</v>
+        <v>13.4164722722449</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.221239586335935</v>
+        <v>0.2255591312302242</v>
       </c>
       <c r="T63">
-        <v>2.286565936338998</v>
+        <v>2.34286408672825</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.247788134363416</v>
+        <v>2.211533487034974</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1256590698674852</v>
+        <v>0.1257324010639557</v>
       </c>
       <c r="C64">
-        <v>84.10235421554719</v>
+        <v>81.86910022995249</v>
       </c>
       <c r="D64">
-        <v>200.8403542155472</v>
+        <v>200.6561002299525</v>
       </c>
       <c r="E64">
-        <v>15.93799999999999</v>
+        <v>17.98699999999999</v>
       </c>
       <c r="F64">
-        <v>127.038</v>
+        <v>129.087</v>
       </c>
       <c r="G64">
         <v>10.3</v>
@@ -6535,28 +6535,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M64">
-        <v>9.6294804</v>
+        <v>9.7847946</v>
       </c>
       <c r="N64">
-        <v>11.66643796734694</v>
+        <v>11.51112376734694</v>
       </c>
       <c r="O64">
-        <v>1.749965695102041</v>
+        <v>1.726668565102041</v>
       </c>
       <c r="P64">
-        <v>9.916472272244897</v>
+        <v>9.784455202244899</v>
       </c>
       <c r="Q64">
-        <v>13.4164722722449</v>
+        <v>13.2844552022449</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2255591312302242</v>
+        <v>0.2301121650377182</v>
       </c>
       <c r="T64">
-        <v>2.34286408672825</v>
+        <v>2.402205380381786</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.211533487034974</v>
+        <v>2.176429780891562</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1257324010639557</v>
+        <v>0.1258057322604263</v>
       </c>
       <c r="C65">
-        <v>81.86910022995249</v>
+        <v>79.63618400928621</v>
       </c>
       <c r="D65">
-        <v>200.6561002299525</v>
+        <v>200.4721840092862</v>
       </c>
       <c r="E65">
-        <v>17.98699999999999</v>
+        <v>20.036</v>
       </c>
       <c r="F65">
-        <v>129.087</v>
+        <v>131.136</v>
       </c>
       <c r="G65">
         <v>10.3</v>
@@ -6617,28 +6617,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M65">
-        <v>9.7847946</v>
+        <v>9.940108800000001</v>
       </c>
       <c r="N65">
-        <v>11.51112376734694</v>
+        <v>11.35580956734694</v>
       </c>
       <c r="O65">
-        <v>1.726668565102041</v>
+        <v>1.703371435102041</v>
       </c>
       <c r="P65">
-        <v>9.784455202244899</v>
+        <v>9.652438132244898</v>
       </c>
       <c r="Q65">
-        <v>13.2844552022449</v>
+        <v>13.1524381322449</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2301121650377182</v>
+        <v>0.2349181451678508</v>
       </c>
       <c r="T65">
-        <v>2.402205380381786</v>
+        <v>2.46484341257163</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.176429780891562</v>
+        <v>2.142423065565131</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1258057322604263</v>
+        <v>0.1258790634568968</v>
       </c>
       <c r="C66">
-        <v>79.63618400928621</v>
+        <v>77.40360462563896</v>
       </c>
       <c r="D66">
-        <v>200.4721840092862</v>
+        <v>200.288604625639</v>
       </c>
       <c r="E66">
-        <v>20.036</v>
+        <v>22.08500000000001</v>
       </c>
       <c r="F66">
-        <v>131.136</v>
+        <v>133.185</v>
       </c>
       <c r="G66">
         <v>10.3</v>
@@ -6699,28 +6699,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M66">
-        <v>9.940108800000001</v>
+        <v>10.095423</v>
       </c>
       <c r="N66">
-        <v>11.35580956734694</v>
+        <v>11.20049536734694</v>
       </c>
       <c r="O66">
-        <v>1.703371435102041</v>
+        <v>1.680074305102041</v>
       </c>
       <c r="P66">
-        <v>9.652438132244898</v>
+        <v>9.520421062244898</v>
       </c>
       <c r="Q66">
-        <v>13.1524381322449</v>
+        <v>13.0204210622449</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2349181451678508</v>
+        <v>0.2399987527339909</v>
       </c>
       <c r="T66">
-        <v>2.46484341257163</v>
+        <v>2.531060760886608</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.142423065565131</v>
+        <v>2.109462710710283</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1258790634568968</v>
+        <v>0.1259523946533673</v>
       </c>
       <c r="C67">
-        <v>77.40360462563896</v>
+        <v>75.17136115449725</v>
       </c>
       <c r="D67">
-        <v>200.288604625639</v>
+        <v>200.1053611544972</v>
       </c>
       <c r="E67">
-        <v>22.08500000000001</v>
+        <v>24.13399999999999</v>
       </c>
       <c r="F67">
-        <v>133.185</v>
+        <v>135.234</v>
       </c>
       <c r="G67">
         <v>10.3</v>
@@ -6781,28 +6781,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M67">
-        <v>10.095423</v>
+        <v>10.2507372</v>
       </c>
       <c r="N67">
-        <v>11.20049536734694</v>
+        <v>11.04518116734694</v>
       </c>
       <c r="O67">
-        <v>1.680074305102041</v>
+        <v>1.656777175102041</v>
       </c>
       <c r="P67">
-        <v>9.520421062244898</v>
+        <v>9.388403992244898</v>
       </c>
       <c r="Q67">
-        <v>13.0204210622449</v>
+        <v>12.8884039922449</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2399987527339909</v>
+        <v>0.2453782195687275</v>
       </c>
       <c r="T67">
-        <v>2.531060760886608</v>
+        <v>2.60117324733776</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.109462710710283</v>
+        <v>2.0775011544874</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1259523946533673</v>
+        <v>0.1260257258498378</v>
       </c>
       <c r="C68">
-        <v>75.17136115449725</v>
+        <v>72.93945267472742</v>
       </c>
       <c r="D68">
-        <v>200.1053611544972</v>
+        <v>199.9224526747274</v>
       </c>
       <c r="E68">
-        <v>24.13399999999999</v>
+        <v>26.18299999999999</v>
       </c>
       <c r="F68">
-        <v>135.234</v>
+        <v>137.283</v>
       </c>
       <c r="G68">
         <v>10.3</v>
@@ -6863,28 +6863,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M68">
-        <v>10.2507372</v>
+        <v>10.4060514</v>
       </c>
       <c r="N68">
-        <v>11.04518116734694</v>
+        <v>10.88986696734694</v>
       </c>
       <c r="O68">
-        <v>1.656777175102041</v>
+        <v>1.633480045102041</v>
       </c>
       <c r="P68">
-        <v>9.388403992244898</v>
+        <v>9.256386922244898</v>
       </c>
       <c r="Q68">
-        <v>12.8884039922449</v>
+        <v>12.7563869222449</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2453782195687275</v>
+        <v>0.2510837146964784</v>
       </c>
       <c r="T68">
-        <v>2.60117324733776</v>
+        <v>2.675534975392013</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.0775011544874</v>
+        <v>2.046493674569678</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1260257258498378</v>
+        <v>0.1260990570463084</v>
       </c>
       <c r="C69">
-        <v>72.93945267472742</v>
+        <v>70.70787826856085</v>
       </c>
       <c r="D69">
-        <v>199.9224526747274</v>
+        <v>199.7398782685608</v>
       </c>
       <c r="E69">
-        <v>26.18299999999999</v>
+        <v>28.232</v>
       </c>
       <c r="F69">
-        <v>137.283</v>
+        <v>139.332</v>
       </c>
       <c r="G69">
         <v>10.3</v>
@@ -6945,28 +6945,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M69">
-        <v>10.4060514</v>
+        <v>10.5613656</v>
       </c>
       <c r="N69">
-        <v>10.88986696734694</v>
+        <v>10.73455276734694</v>
       </c>
       <c r="O69">
-        <v>1.633480045102041</v>
+        <v>1.610182915102041</v>
       </c>
       <c r="P69">
-        <v>9.256386922244898</v>
+        <v>9.124369852244898</v>
       </c>
       <c r="Q69">
-        <v>12.7563869222449</v>
+        <v>12.6243698522449</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2510837146964784</v>
+        <v>0.2571458032697138</v>
       </c>
       <c r="T69">
-        <v>2.675534975392013</v>
+        <v>2.754544311449656</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.046493674569678</v>
+        <v>2.016398179355418</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1260990570463084</v>
+        <v>0.1345006882427789</v>
       </c>
       <c r="C70">
-        <v>70.70787826856085</v>
+        <v>49.73973766564689</v>
       </c>
       <c r="D70">
-        <v>199.7398782685608</v>
+        <v>180.8207376656469</v>
       </c>
       <c r="E70">
-        <v>28.232</v>
+        <v>30.28100000000001</v>
       </c>
       <c r="F70">
-        <v>139.332</v>
+        <v>141.381</v>
       </c>
       <c r="G70">
         <v>10.3</v>
@@ -7027,45 +7027,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M70">
-        <v>10.5613656</v>
+        <v>12.72429</v>
       </c>
       <c r="N70">
-        <v>10.73455276734694</v>
+        <v>8.571628367346939</v>
       </c>
       <c r="O70">
-        <v>1.610182915102041</v>
+        <v>1.285744255102041</v>
       </c>
       <c r="P70">
-        <v>9.124369852244898</v>
+        <v>7.285884112244898</v>
       </c>
       <c r="Q70">
-        <v>12.6243698522449</v>
+        <v>10.7858841122449</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2571458032697138</v>
+        <v>0.263598994331545</v>
       </c>
       <c r="T70">
-        <v>2.754544311449656</v>
+        <v>2.838651024027148</v>
       </c>
       <c r="U70">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V70">
         <v>0.15</v>
       </c>
       <c r="W70">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.016398179355418</v>
+        <v>1.673642959045019</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1345006882427789</v>
+        <v>0.1346947194392495</v>
       </c>
       <c r="C71">
-        <v>49.73973766564689</v>
+        <v>47.29605883323407</v>
       </c>
       <c r="D71">
-        <v>180.8207376656469</v>
+        <v>180.4260588332341</v>
       </c>
       <c r="E71">
-        <v>30.28100000000001</v>
+        <v>32.33000000000001</v>
       </c>
       <c r="F71">
-        <v>141.381</v>
+        <v>143.43</v>
       </c>
       <c r="G71">
         <v>10.3</v>
@@ -7109,28 +7109,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M71">
-        <v>12.72429</v>
+        <v>12.9087</v>
       </c>
       <c r="N71">
-        <v>8.571628367346939</v>
+        <v>8.387218367346939</v>
       </c>
       <c r="O71">
-        <v>1.285744255102041</v>
+        <v>1.258082755102041</v>
       </c>
       <c r="P71">
-        <v>7.285884112244898</v>
+        <v>7.129135612244898</v>
       </c>
       <c r="Q71">
-        <v>10.7858841122449</v>
+        <v>10.6291356122449</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.263598994331545</v>
+        <v>0.2704823981308315</v>
       </c>
       <c r="T71">
-        <v>2.838651024027148</v>
+        <v>2.928364850776472</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.673642959045019</v>
+        <v>1.649733773915804</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1346947194392495</v>
+        <v>0.13488875063572</v>
       </c>
       <c r="C72">
-        <v>47.29605883323407</v>
+        <v>44.85409918546642</v>
       </c>
       <c r="D72">
-        <v>180.4260588332341</v>
+        <v>180.0330991854664</v>
       </c>
       <c r="E72">
-        <v>32.33000000000001</v>
+        <v>34.37900000000002</v>
       </c>
       <c r="F72">
-        <v>143.43</v>
+        <v>145.479</v>
       </c>
       <c r="G72">
         <v>10.3</v>
@@ -7191,28 +7191,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M72">
-        <v>12.9087</v>
+        <v>13.09311</v>
       </c>
       <c r="N72">
-        <v>8.387218367346939</v>
+        <v>8.202808367346938</v>
       </c>
       <c r="O72">
-        <v>1.258082755102041</v>
+        <v>1.230421255102041</v>
       </c>
       <c r="P72">
-        <v>7.129135612244898</v>
+        <v>6.972387112244897</v>
       </c>
       <c r="Q72">
-        <v>10.6291356122449</v>
+        <v>10.4723871122449</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2704823981308315</v>
+        <v>0.2778405194335173</v>
       </c>
       <c r="T72">
-        <v>2.928364850776472</v>
+        <v>3.024265837991268</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.649733773915804</v>
+        <v>1.626498086959243</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.13488875063572</v>
+        <v>0.1350827818321905</v>
       </c>
       <c r="C73">
-        <v>44.85409918546645</v>
+        <v>42.41384751384052</v>
       </c>
       <c r="D73">
-        <v>180.0330991854664</v>
+        <v>179.6418475138405</v>
       </c>
       <c r="E73">
-        <v>34.37899999999999</v>
+        <v>36.428</v>
       </c>
       <c r="F73">
-        <v>145.479</v>
+        <v>147.528</v>
       </c>
       <c r="G73">
         <v>10.3</v>
@@ -7273,28 +7273,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M73">
-        <v>13.09311</v>
+        <v>13.27752</v>
       </c>
       <c r="N73">
-        <v>8.202808367346941</v>
+        <v>8.01839836734694</v>
       </c>
       <c r="O73">
-        <v>1.230421255102041</v>
+        <v>1.202759755102041</v>
       </c>
       <c r="P73">
-        <v>6.9723871122449</v>
+        <v>6.815638612244899</v>
       </c>
       <c r="Q73">
-        <v>10.4723871122449</v>
+        <v>10.3156386122449</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2778405194335172</v>
+        <v>0.2857242208292519</v>
       </c>
       <c r="T73">
-        <v>3.024265837991266</v>
+        <v>3.127016895721404</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.626498086959244</v>
+        <v>1.603907835751476</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1350827818321905</v>
+        <v>0.135276813028661</v>
       </c>
       <c r="C74">
-        <v>42.41384751384052</v>
+        <v>39.97529270707605</v>
       </c>
       <c r="D74">
-        <v>179.6418475138405</v>
+        <v>179.252292707076</v>
       </c>
       <c r="E74">
-        <v>36.428</v>
+        <v>38.47699999999998</v>
       </c>
       <c r="F74">
-        <v>147.528</v>
+        <v>149.577</v>
       </c>
       <c r="G74">
         <v>10.3</v>
@@ -7355,28 +7355,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M74">
-        <v>13.27752</v>
+        <v>13.46193</v>
       </c>
       <c r="N74">
-        <v>8.01839836734694</v>
+        <v>7.833988367346942</v>
       </c>
       <c r="O74">
-        <v>1.202759755102041</v>
+        <v>1.175098255102041</v>
       </c>
       <c r="P74">
-        <v>6.815638612244899</v>
+        <v>6.658890112244901</v>
       </c>
       <c r="Q74">
-        <v>10.3156386122449</v>
+        <v>10.1588901122449</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2857242208292519</v>
+        <v>0.294191900106152</v>
       </c>
       <c r="T74">
-        <v>3.127016895721404</v>
+        <v>3.237379142913033</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.603907835751476</v>
+        <v>1.581936495535703</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.135276813028661</v>
+        <v>0.1354708442251316</v>
       </c>
       <c r="C75">
-        <v>39.97529270707605</v>
+        <v>37.5384237500634</v>
       </c>
       <c r="D75">
-        <v>179.252292707076</v>
+        <v>178.8644237500634</v>
       </c>
       <c r="E75">
-        <v>38.47699999999998</v>
+        <v>40.52599999999998</v>
       </c>
       <c r="F75">
-        <v>149.577</v>
+        <v>151.626</v>
       </c>
       <c r="G75">
         <v>10.3</v>
@@ -7437,28 +7437,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M75">
-        <v>13.46193</v>
+        <v>13.64634</v>
       </c>
       <c r="N75">
-        <v>7.833988367346942</v>
+        <v>7.649578367346942</v>
       </c>
       <c r="O75">
-        <v>1.175098255102041</v>
+        <v>1.147436755102041</v>
       </c>
       <c r="P75">
-        <v>6.658890112244901</v>
+        <v>6.502141612244901</v>
       </c>
       <c r="Q75">
-        <v>10.1588901122449</v>
+        <v>10.0021416122449</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.294191900106152</v>
+        <v>0.3033109393274291</v>
       </c>
       <c r="T75">
-        <v>3.237379142913033</v>
+        <v>3.356230793734787</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.581936495535703</v>
+        <v>1.560558975325761</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1354708442251316</v>
+        <v>0.1356648754216021</v>
       </c>
       <c r="C76">
-        <v>37.5384237500634</v>
+        <v>35.10322972282626</v>
       </c>
       <c r="D76">
-        <v>178.8644237500634</v>
+        <v>178.4782297228262</v>
       </c>
       <c r="E76">
-        <v>40.52599999999998</v>
+        <v>42.57499999999999</v>
       </c>
       <c r="F76">
-        <v>151.626</v>
+        <v>153.675</v>
       </c>
       <c r="G76">
         <v>10.3</v>
@@ -7519,28 +7519,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M76">
-        <v>13.64634</v>
+        <v>13.83075</v>
       </c>
       <c r="N76">
-        <v>7.649578367346942</v>
+        <v>7.465168367346941</v>
       </c>
       <c r="O76">
-        <v>1.147436755102041</v>
+        <v>1.119775255102041</v>
       </c>
       <c r="P76">
-        <v>6.502141612244901</v>
+        <v>6.345393112244899</v>
       </c>
       <c r="Q76">
-        <v>10.0021416122449</v>
+        <v>9.845393112244899</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3033109393274291</v>
+        <v>0.3131595016864084</v>
       </c>
       <c r="T76">
-        <v>3.356230793734787</v>
+        <v>3.484590576622282</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.560558975325761</v>
+        <v>1.539751522321417</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1356648754216021</v>
+        <v>0.1358589066180727</v>
       </c>
       <c r="C77">
-        <v>35.10322972282626</v>
+        <v>32.66969979949587</v>
       </c>
       <c r="D77">
-        <v>178.4782297228262</v>
+        <v>178.0936997994959</v>
       </c>
       <c r="E77">
-        <v>42.57499999999999</v>
+        <v>44.624</v>
       </c>
       <c r="F77">
-        <v>153.675</v>
+        <v>155.724</v>
       </c>
       <c r="G77">
         <v>10.3</v>
@@ -7601,28 +7601,28 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M77">
-        <v>13.83075</v>
+        <v>14.01516</v>
       </c>
       <c r="N77">
-        <v>7.465168367346941</v>
+        <v>7.280758367346941</v>
       </c>
       <c r="O77">
-        <v>1.119775255102041</v>
+        <v>1.092113755102041</v>
       </c>
       <c r="P77">
-        <v>6.345393112244899</v>
+        <v>6.1886446122449</v>
       </c>
       <c r="Q77">
-        <v>9.845393112244899</v>
+        <v>9.6886446122449</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3131595016864084</v>
+        <v>0.3238287775753028</v>
       </c>
       <c r="T77">
-        <v>3.484590576622282</v>
+        <v>3.623647008083735</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.539751522321417</v>
+        <v>1.51949163386982</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1358589066180727</v>
+        <v>0.1752944504419975</v>
       </c>
       <c r="C78">
-        <v>32.66969979949587</v>
+        <v>-23.61499817239326</v>
       </c>
       <c r="D78">
-        <v>178.0936997994959</v>
+        <v>123.8580018276067</v>
       </c>
       <c r="E78">
-        <v>44.624</v>
+        <v>46.673</v>
       </c>
       <c r="F78">
-        <v>155.724</v>
+        <v>157.773</v>
       </c>
       <c r="G78">
         <v>10.3</v>
@@ -7683,45 +7683,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M78">
-        <v>14.01516</v>
+        <v>23.1610764</v>
       </c>
       <c r="N78">
-        <v>7.280758367346941</v>
+        <v>-1.865158032653063</v>
       </c>
       <c r="O78">
-        <v>1.092113755102041</v>
+        <v>-0.2797737048979595</v>
       </c>
       <c r="P78">
-        <v>6.1886446122449</v>
+        <v>-1.585384327755104</v>
       </c>
       <c r="Q78">
-        <v>9.6886446122449</v>
+        <v>1.914615672244896</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3238287775753028</v>
+        <v>0.3384714548065298</v>
       </c>
       <c r="T78">
-        <v>3.623647008083735</v>
+        <v>3.814490179074914</v>
       </c>
       <c r="U78">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.15</v>
+        <v>0.137920522342478</v>
       </c>
       <c r="W78">
-        <v>0.0765</v>
+        <v>0.1265532673201243</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.51949163386982</v>
+        <v>0.9194701489498535</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1752944504419975</v>
+        <v>0.1763044504419975</v>
       </c>
       <c r="C79">
-        <v>-23.61499817239326</v>
+        <v>-26.6225599794596</v>
       </c>
       <c r="D79">
-        <v>123.8580018276067</v>
+        <v>122.8994400205404</v>
       </c>
       <c r="E79">
-        <v>46.673</v>
+        <v>48.72199999999998</v>
       </c>
       <c r="F79">
-        <v>157.773</v>
+        <v>159.822</v>
       </c>
       <c r="G79">
         <v>10.3</v>
@@ -7765,37 +7765,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M79">
-        <v>23.1610764</v>
+        <v>23.4618696</v>
       </c>
       <c r="N79">
-        <v>-1.865158032653063</v>
+        <v>-2.165951232653061</v>
       </c>
       <c r="O79">
-        <v>-0.2797737048979595</v>
+        <v>-0.3248926848979591</v>
       </c>
       <c r="P79">
-        <v>-1.585384327755104</v>
+        <v>-1.841058547755102</v>
       </c>
       <c r="Q79">
-        <v>1.914615672244896</v>
+        <v>1.658941452244898</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3384714548065298</v>
+        <v>0.3517747027522812</v>
       </c>
       <c r="T79">
-        <v>3.814490179074914</v>
+        <v>3.987876096305592</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.137920522342478</v>
+        <v>0.1361523105175745</v>
       </c>
       <c r="W79">
-        <v>0.1265532673201243</v>
+        <v>0.1268128408160201</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9194701489498535</v>
+        <v>0.9076820701171632</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1763044504419975</v>
+        <v>0.1773144504419975</v>
       </c>
       <c r="C80">
-        <v>-26.6225599794596</v>
+        <v>-29.61539872876489</v>
       </c>
       <c r="D80">
-        <v>122.8994400205404</v>
+        <v>121.9556012712351</v>
       </c>
       <c r="E80">
-        <v>48.72199999999998</v>
+        <v>50.77099999999999</v>
       </c>
       <c r="F80">
-        <v>159.822</v>
+        <v>161.871</v>
       </c>
       <c r="G80">
         <v>10.3</v>
@@ -7847,37 +7847,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M80">
-        <v>23.4618696</v>
+        <v>23.7626628</v>
       </c>
       <c r="N80">
-        <v>-2.165951232653061</v>
+        <v>-2.466744432653062</v>
       </c>
       <c r="O80">
-        <v>-0.3248926848979591</v>
+        <v>-0.3700116648979593</v>
       </c>
       <c r="P80">
-        <v>-1.841058547755102</v>
+        <v>-2.096732767755103</v>
       </c>
       <c r="Q80">
-        <v>1.658941452244898</v>
+        <v>1.403267232244897</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3517747027522812</v>
+        <v>0.3663449266928661</v>
       </c>
       <c r="T80">
-        <v>3.987876096305592</v>
+        <v>4.17777495803443</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1361523105175745</v>
+        <v>0.1344288635489976</v>
       </c>
       <c r="W80">
-        <v>0.1268128408160201</v>
+        <v>0.1270658428310072</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9076820701171632</v>
+        <v>0.8961924236599839</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1773144504419975</v>
+        <v>0.1783244504419975</v>
       </c>
       <c r="C81">
-        <v>-29.61539872876489</v>
+        <v>-32.59385104396506</v>
       </c>
       <c r="D81">
-        <v>121.9556012712351</v>
+        <v>121.0261489560349</v>
       </c>
       <c r="E81">
-        <v>50.77099999999999</v>
+        <v>52.81999999999999</v>
       </c>
       <c r="F81">
-        <v>161.871</v>
+        <v>163.92</v>
       </c>
       <c r="G81">
         <v>10.3</v>
@@ -7929,37 +7929,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M81">
-        <v>23.7626628</v>
+        <v>24.063456</v>
       </c>
       <c r="N81">
-        <v>-2.466744432653062</v>
+        <v>-2.767537632653063</v>
       </c>
       <c r="O81">
-        <v>-0.3700116648979593</v>
+        <v>-0.4151306448979595</v>
       </c>
       <c r="P81">
-        <v>-2.096732767755103</v>
+        <v>-2.352406987755104</v>
       </c>
       <c r="Q81">
-        <v>1.403267232244897</v>
+        <v>1.147593012244896</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3663449266928661</v>
+        <v>0.3823721730275094</v>
       </c>
       <c r="T81">
-        <v>4.17777495803443</v>
+        <v>4.386663705936152</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1344288635489976</v>
+        <v>0.1327485027546351</v>
       </c>
       <c r="W81">
-        <v>0.1270658428310072</v>
+        <v>0.1273125197956196</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8961924236599839</v>
+        <v>0.884990018364234</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1783244504419975</v>
+        <v>0.1793344504419975</v>
       </c>
       <c r="C82">
-        <v>-32.59385104396506</v>
+        <v>-35.55824336438121</v>
       </c>
       <c r="D82">
-        <v>121.0261489560349</v>
+        <v>120.1107566356188</v>
       </c>
       <c r="E82">
-        <v>52.81999999999999</v>
+        <v>54.869</v>
       </c>
       <c r="F82">
-        <v>163.92</v>
+        <v>165.969</v>
       </c>
       <c r="G82">
         <v>10.3</v>
@@ -8011,37 +8011,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M82">
-        <v>24.063456</v>
+        <v>24.3642492</v>
       </c>
       <c r="N82">
-        <v>-2.767537632653063</v>
+        <v>-3.068330832653061</v>
       </c>
       <c r="O82">
-        <v>-0.4151306448979595</v>
+        <v>-0.4602496248979591</v>
       </c>
       <c r="P82">
-        <v>-2.352406987755104</v>
+        <v>-2.608081207755101</v>
       </c>
       <c r="Q82">
-        <v>1.147593012244896</v>
+        <v>0.8919187922448986</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3823721730275094</v>
+        <v>0.4000864979236941</v>
       </c>
       <c r="T82">
-        <v>4.386663705936152</v>
+        <v>4.617540743090687</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1327485027546351</v>
+        <v>0.1311096323502569</v>
       </c>
       <c r="W82">
-        <v>0.1273125197956196</v>
+        <v>0.1275531059709823</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.884990018364234</v>
+        <v>0.8740642156683793</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1793344504419975</v>
+        <v>0.1803444504419975</v>
       </c>
       <c r="C83">
-        <v>-35.55824336438121</v>
+        <v>-38.50889232725893</v>
       </c>
       <c r="D83">
-        <v>120.1107566356188</v>
+        <v>119.2091076727411</v>
       </c>
       <c r="E83">
-        <v>54.869</v>
+        <v>56.91800000000001</v>
       </c>
       <c r="F83">
-        <v>165.969</v>
+        <v>168.018</v>
       </c>
       <c r="G83">
         <v>10.3</v>
@@ -8093,37 +8093,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M83">
-        <v>24.3642492</v>
+        <v>24.6650424</v>
       </c>
       <c r="N83">
-        <v>-3.068330832653061</v>
+        <v>-3.369124032653062</v>
       </c>
       <c r="O83">
-        <v>-0.4602496248979591</v>
+        <v>-0.5053686048979592</v>
       </c>
       <c r="P83">
-        <v>-2.608081207755101</v>
+        <v>-2.863755427755103</v>
       </c>
       <c r="Q83">
-        <v>0.8919187922448986</v>
+        <v>0.6362445722448973</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4000864979236941</v>
+        <v>0.4197690811416772</v>
       </c>
       <c r="T83">
-        <v>4.617540743090687</v>
+        <v>4.874070784373503</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1311096323502569</v>
+        <v>0.129510734394766</v>
       </c>
       <c r="W83">
-        <v>0.1275531059709823</v>
+        <v>0.1277878241908484</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8740642156683793</v>
+        <v>0.8634048959651064</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1803444504419975</v>
+        <v>0.1813544504419975</v>
       </c>
       <c r="C84">
-        <v>-38.50889232725893</v>
+        <v>-41.4461051329387</v>
       </c>
       <c r="D84">
-        <v>119.2091076727411</v>
+        <v>118.3208948670613</v>
       </c>
       <c r="E84">
-        <v>56.91800000000001</v>
+        <v>58.96700000000001</v>
       </c>
       <c r="F84">
-        <v>168.018</v>
+        <v>170.067</v>
       </c>
       <c r="G84">
         <v>10.3</v>
@@ -8175,37 +8175,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M84">
-        <v>24.6650424</v>
+        <v>24.9658356</v>
       </c>
       <c r="N84">
-        <v>-3.369124032653062</v>
+        <v>-3.669917232653063</v>
       </c>
       <c r="O84">
-        <v>-0.5053686048979592</v>
+        <v>-0.5504875848979595</v>
       </c>
       <c r="P84">
-        <v>-2.863755427755103</v>
+        <v>-3.119429647755104</v>
       </c>
       <c r="Q84">
-        <v>0.6362445722448973</v>
+        <v>0.3805703522448964</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4197690811416772</v>
+        <v>0.4417672623853052</v>
       </c>
       <c r="T84">
-        <v>4.874070784373503</v>
+        <v>5.16078083051312</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.129510734394766</v>
+        <v>0.1279503641008531</v>
       </c>
       <c r="W84">
-        <v>0.1277878241908484</v>
+        <v>0.1280168865499948</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8634048959651064</v>
+        <v>0.8530024273390208</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1813544504419975</v>
+        <v>0.1823644504419976</v>
       </c>
       <c r="C85">
-        <v>-41.4461051329387</v>
+        <v>-44.37017989382234</v>
       </c>
       <c r="D85">
-        <v>118.3208948670613</v>
+        <v>117.4458201061776</v>
       </c>
       <c r="E85">
-        <v>58.96700000000001</v>
+        <v>61.01599999999999</v>
       </c>
       <c r="F85">
-        <v>170.067</v>
+        <v>172.116</v>
       </c>
       <c r="G85">
         <v>10.3</v>
@@ -8257,37 +8257,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M85">
-        <v>24.9658356</v>
+        <v>25.2666288</v>
       </c>
       <c r="N85">
-        <v>-3.669917232653063</v>
+        <v>-3.97071043265306</v>
       </c>
       <c r="O85">
-        <v>-0.5504875848979595</v>
+        <v>-0.595606564897959</v>
       </c>
       <c r="P85">
-        <v>-3.119429647755104</v>
+        <v>-3.375103867755101</v>
       </c>
       <c r="Q85">
-        <v>0.3805703522448964</v>
+        <v>0.1248961322448987</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4417672623853052</v>
+        <v>0.4665152162843869</v>
       </c>
       <c r="T85">
-        <v>5.16078083051312</v>
+        <v>5.483329632420192</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1279503641008531</v>
+        <v>0.1264271454806049</v>
       </c>
       <c r="W85">
-        <v>0.1280168865499948</v>
+        <v>0.1282404950434472</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8530024273390208</v>
+        <v>0.8428476365373658</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1823644504419976</v>
+        <v>0.1833744504419975</v>
       </c>
       <c r="C86">
-        <v>-44.37017989382234</v>
+        <v>-47.28140596796712</v>
       </c>
       <c r="D86">
-        <v>117.4458201061776</v>
+        <v>116.5835940320328</v>
       </c>
       <c r="E86">
-        <v>61.01599999999999</v>
+        <v>63.06499999999997</v>
       </c>
       <c r="F86">
-        <v>172.116</v>
+        <v>174.165</v>
       </c>
       <c r="G86">
         <v>10.3</v>
@@ -8339,37 +8339,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M86">
-        <v>25.2666288</v>
+        <v>25.567422</v>
       </c>
       <c r="N86">
-        <v>-3.97071043265306</v>
+        <v>-4.271503632653058</v>
       </c>
       <c r="O86">
-        <v>-0.595606564897959</v>
+        <v>-0.6407255448979586</v>
       </c>
       <c r="P86">
-        <v>-3.375103867755101</v>
+        <v>-3.630778087755099</v>
       </c>
       <c r="Q86">
-        <v>0.1248961322448987</v>
+        <v>-0.1307780877550995</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4665152162843866</v>
+        <v>0.4945628973700124</v>
       </c>
       <c r="T86">
-        <v>5.483329632420189</v>
+        <v>5.8488849412482</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1264271454806049</v>
+        <v>0.1249397672984801</v>
       </c>
       <c r="W86">
-        <v>0.1282404950434472</v>
+        <v>0.1284588421605831</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8428476365373658</v>
+        <v>0.8329317819898675</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1833744504419975</v>
+        <v>0.1843844504419975</v>
       </c>
       <c r="C87">
-        <v>-47.28140596796712</v>
+        <v>-50.1800642780936</v>
       </c>
       <c r="D87">
-        <v>116.5835940320328</v>
+        <v>115.7339357219064</v>
       </c>
       <c r="E87">
-        <v>63.06499999999997</v>
+        <v>65.11399999999998</v>
       </c>
       <c r="F87">
-        <v>174.165</v>
+        <v>176.214</v>
       </c>
       <c r="G87">
         <v>10.3</v>
@@ -8421,37 +8421,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M87">
-        <v>25.567422</v>
+        <v>25.8682152</v>
       </c>
       <c r="N87">
-        <v>-4.271503632653058</v>
+        <v>-4.572296832653059</v>
       </c>
       <c r="O87">
-        <v>-0.6407255448979586</v>
+        <v>-0.6858445248979589</v>
       </c>
       <c r="P87">
-        <v>-3.630778087755099</v>
+        <v>-3.8864523077551</v>
       </c>
       <c r="Q87">
-        <v>-0.1307780877550995</v>
+        <v>-0.3864523077551003</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4945628973700124</v>
+        <v>0.526617390039299</v>
       </c>
       <c r="T87">
-        <v>5.8488849412482</v>
+        <v>6.266662437051644</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1249397672984801</v>
+        <v>0.1234869793066373</v>
       </c>
       <c r="W87">
-        <v>0.1284588421605831</v>
+        <v>0.1286721114377856</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8329317819898675</v>
+        <v>0.8232465287109155</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1843844504419975</v>
+        <v>0.1853944504419975</v>
       </c>
       <c r="C88">
-        <v>-50.1800642780936</v>
+        <v>-53.06642761674361</v>
       </c>
       <c r="D88">
-        <v>115.7339357219064</v>
+        <v>114.8965723832564</v>
       </c>
       <c r="E88">
-        <v>65.11399999999998</v>
+        <v>67.16299999999998</v>
       </c>
       <c r="F88">
-        <v>176.214</v>
+        <v>178.263</v>
       </c>
       <c r="G88">
         <v>10.3</v>
@@ -8503,37 +8503,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M88">
-        <v>25.8682152</v>
+        <v>26.1690084</v>
       </c>
       <c r="N88">
-        <v>-4.572296832653059</v>
+        <v>-4.87309003265306</v>
       </c>
       <c r="O88">
-        <v>-0.6858445248979589</v>
+        <v>-0.730963504897959</v>
       </c>
       <c r="P88">
-        <v>-3.8864523077551</v>
+        <v>-4.142126527755101</v>
       </c>
       <c r="Q88">
-        <v>-0.3864523077551003</v>
+        <v>-0.6421265277551012</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.526617390039299</v>
+        <v>0.563603343119245</v>
       </c>
       <c r="T88">
-        <v>6.266662437051644</v>
+        <v>6.748713393747924</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1234869793066373</v>
+        <v>0.1220675887398944</v>
       </c>
       <c r="W88">
-        <v>0.1286721114377856</v>
+        <v>0.1288804779729835</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8232465287109155</v>
+        <v>0.8137839249326291</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1853944504419975</v>
+        <v>0.1864044504419975</v>
       </c>
       <c r="C89">
-        <v>-53.06642761674361</v>
+        <v>-55.94076093828713</v>
       </c>
       <c r="D89">
-        <v>114.8965723832564</v>
+        <v>114.0712390617129</v>
       </c>
       <c r="E89">
-        <v>67.16299999999998</v>
+        <v>69.21199999999999</v>
       </c>
       <c r="F89">
-        <v>178.263</v>
+        <v>180.312</v>
       </c>
       <c r="G89">
         <v>10.3</v>
@@ -8585,37 +8585,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M89">
-        <v>26.1690084</v>
+        <v>26.4698016</v>
       </c>
       <c r="N89">
-        <v>-4.87309003265306</v>
+        <v>-5.173883232653061</v>
       </c>
       <c r="O89">
-        <v>-0.730963504897959</v>
+        <v>-0.7760824848979592</v>
       </c>
       <c r="P89">
-        <v>-4.142126527755101</v>
+        <v>-4.397800747755102</v>
       </c>
       <c r="Q89">
-        <v>-0.6421265277551012</v>
+        <v>-0.8978007477551024</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.563603343119245</v>
+        <v>0.6067536217125155</v>
       </c>
       <c r="T89">
-        <v>6.748713393747924</v>
+        <v>7.311106176560252</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1220675887398944</v>
+        <v>0.1206804570496683</v>
       </c>
       <c r="W89">
-        <v>0.1288804779729835</v>
+        <v>0.1290841089051087</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8137839249326291</v>
+        <v>0.8045363803311218</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1864044504419975</v>
+        <v>0.2376253341987892</v>
       </c>
       <c r="C90">
-        <v>-55.94076093828713</v>
+        <v>-88.44887469600509</v>
       </c>
       <c r="D90">
-        <v>114.0712390617129</v>
+        <v>83.6121253039949</v>
       </c>
       <c r="E90">
-        <v>69.21199999999999</v>
+        <v>71.261</v>
       </c>
       <c r="F90">
-        <v>180.312</v>
+        <v>182.361</v>
       </c>
       <c r="G90">
         <v>10.3</v>
@@ -8667,45 +8667,45 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M90">
-        <v>26.4698016</v>
+        <v>36.6180888</v>
       </c>
       <c r="N90">
-        <v>-5.173883232653061</v>
+        <v>-15.32217043265306</v>
       </c>
       <c r="O90">
-        <v>-0.7760824848979592</v>
+        <v>-2.298325564897959</v>
       </c>
       <c r="P90">
-        <v>-4.397800747755102</v>
+        <v>-13.0238448677551</v>
       </c>
       <c r="Q90">
-        <v>-0.8978007477551024</v>
+        <v>-9.523844867755104</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6067536217125155</v>
+        <v>0.6773028942026682</v>
       </c>
       <c r="T90">
-        <v>7.311106176560252</v>
+        <v>8.230599699536253</v>
       </c>
       <c r="U90">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1206804570496683</v>
+        <v>0.08723523973490503</v>
       </c>
       <c r="W90">
-        <v>0.1290841089051087</v>
+        <v>0.1832831638612311</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.8045363803311218</v>
+        <v>0.5815682648993667</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2376253341987892</v>
+        <v>0.2391753341987892</v>
       </c>
       <c r="C91">
-        <v>-88.44887469600509</v>
+        <v>-91.16806769015379</v>
       </c>
       <c r="D91">
-        <v>83.6121253039949</v>
+        <v>82.94193230984621</v>
       </c>
       <c r="E91">
-        <v>71.261</v>
+        <v>73.31</v>
       </c>
       <c r="F91">
-        <v>182.361</v>
+        <v>184.41</v>
       </c>
       <c r="G91">
         <v>10.3</v>
@@ -8749,37 +8749,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M91">
-        <v>36.6180888</v>
+        <v>37.029528</v>
       </c>
       <c r="N91">
-        <v>-15.32217043265306</v>
+        <v>-15.73360963265306</v>
       </c>
       <c r="O91">
-        <v>-2.298325564897959</v>
+        <v>-2.360041444897959</v>
       </c>
       <c r="P91">
-        <v>-13.0238448677551</v>
+        <v>-13.3735681877551</v>
       </c>
       <c r="Q91">
-        <v>-9.523844867755104</v>
+        <v>-9.873568187755101</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6773028942026682</v>
+        <v>0.740453183622935</v>
       </c>
       <c r="T91">
-        <v>8.230599699536253</v>
+        <v>9.053659669489878</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08723523973490503</v>
+        <v>0.08626595929340608</v>
       </c>
       <c r="W91">
-        <v>0.1832831638612311</v>
+        <v>0.1834777953738841</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5815682648993667</v>
+        <v>0.5751063952893739</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2391753341987892</v>
+        <v>0.2407253341987892</v>
       </c>
       <c r="C92">
-        <v>-91.16806769015379</v>
+        <v>-93.87660225300928</v>
       </c>
       <c r="D92">
-        <v>82.94193230984621</v>
+        <v>82.2823977469907</v>
       </c>
       <c r="E92">
-        <v>73.31</v>
+        <v>75.35899999999998</v>
       </c>
       <c r="F92">
-        <v>184.41</v>
+        <v>186.459</v>
       </c>
       <c r="G92">
         <v>10.3</v>
@@ -8831,37 +8831,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M92">
-        <v>37.029528</v>
+        <v>37.4409672</v>
       </c>
       <c r="N92">
-        <v>-15.73360963265306</v>
+        <v>-16.14504883265306</v>
       </c>
       <c r="O92">
-        <v>-2.360041444897959</v>
+        <v>-2.421757324897958</v>
       </c>
       <c r="P92">
-        <v>-13.3735681877551</v>
+        <v>-13.7232915077551</v>
       </c>
       <c r="Q92">
-        <v>-9.873568187755101</v>
+        <v>-10.2232915077551</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.740453183622935</v>
+        <v>0.8176368706921502</v>
       </c>
       <c r="T92">
-        <v>9.053659669489878</v>
+        <v>10.05962185498876</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08626595929340608</v>
+        <v>0.08531798171875328</v>
       </c>
       <c r="W92">
-        <v>0.1834777953738841</v>
+        <v>0.1836681492708744</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5751063952893739</v>
+        <v>0.5687865447916886</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2407253341987892</v>
+        <v>0.2422753341987892</v>
       </c>
       <c r="C93">
-        <v>-93.87660225300928</v>
+        <v>-96.57473063865588</v>
       </c>
       <c r="D93">
-        <v>82.2823977469907</v>
+        <v>81.63326936134411</v>
       </c>
       <c r="E93">
-        <v>75.35899999999998</v>
+        <v>77.40799999999999</v>
       </c>
       <c r="F93">
-        <v>186.459</v>
+        <v>188.508</v>
       </c>
       <c r="G93">
         <v>10.3</v>
@@ -8913,37 +8913,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M93">
-        <v>37.4409672</v>
+        <v>37.8524064</v>
       </c>
       <c r="N93">
-        <v>-16.14504883265306</v>
+        <v>-16.55648803265306</v>
       </c>
       <c r="O93">
-        <v>-2.421757324897958</v>
+        <v>-2.483473204897959</v>
       </c>
       <c r="P93">
-        <v>-13.7232915077551</v>
+        <v>-14.0730148277551</v>
       </c>
       <c r="Q93">
-        <v>-10.2232915077551</v>
+        <v>-10.5730148277551</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8176368706921502</v>
+        <v>0.9141164795286691</v>
       </c>
       <c r="T93">
-        <v>10.05962185498876</v>
+        <v>11.31707458686235</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08531798171875328</v>
+        <v>0.08439061235224508</v>
       </c>
       <c r="W93">
-        <v>0.1836681492708744</v>
+        <v>0.1838543650396692</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5687865447916886</v>
+        <v>0.5626040823483005</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2422753341987892</v>
+        <v>0.2438253341987892</v>
       </c>
       <c r="C94">
-        <v>-96.57473063865588</v>
+        <v>-99.26269720332313</v>
       </c>
       <c r="D94">
-        <v>81.63326936134411</v>
+        <v>80.99430279667686</v>
       </c>
       <c r="E94">
-        <v>77.40799999999999</v>
+        <v>79.45699999999999</v>
       </c>
       <c r="F94">
-        <v>188.508</v>
+        <v>190.557</v>
       </c>
       <c r="G94">
         <v>10.3</v>
@@ -8995,37 +8995,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M94">
-        <v>37.8524064</v>
+        <v>38.2638456</v>
       </c>
       <c r="N94">
-        <v>-16.55648803265306</v>
+        <v>-16.96792723265306</v>
       </c>
       <c r="O94">
-        <v>-2.483473204897959</v>
+        <v>-2.545189084897959</v>
       </c>
       <c r="P94">
-        <v>-14.0730148277551</v>
+        <v>-14.4227381477551</v>
       </c>
       <c r="Q94">
-        <v>-10.5730148277551</v>
+        <v>-10.9227381477551</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9141164795286691</v>
+        <v>1.038161690889908</v>
       </c>
       <c r="T94">
-        <v>11.31707458686235</v>
+        <v>12.93379952784269</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08439061235224508</v>
+        <v>0.08348318641297364</v>
       </c>
       <c r="W94">
-        <v>0.1838543650396692</v>
+        <v>0.1840365761682749</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5626040823483005</v>
+        <v>0.5565545760864909</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2438253341987892</v>
+        <v>0.2453753341987892</v>
       </c>
       <c r="C95">
-        <v>-99.26269720332313</v>
+        <v>-101.9407387120789</v>
       </c>
       <c r="D95">
-        <v>80.99430279667686</v>
+        <v>80.36526128792107</v>
       </c>
       <c r="E95">
-        <v>79.45699999999999</v>
+        <v>81.506</v>
       </c>
       <c r="F95">
-        <v>190.557</v>
+        <v>192.606</v>
       </c>
       <c r="G95">
         <v>10.3</v>
@@ -9077,37 +9077,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M95">
-        <v>38.2638456</v>
+        <v>38.6752848</v>
       </c>
       <c r="N95">
-        <v>-16.96792723265306</v>
+        <v>-17.37936643265306</v>
       </c>
       <c r="O95">
-        <v>-2.545189084897959</v>
+        <v>-2.606904964897959</v>
       </c>
       <c r="P95">
-        <v>-14.4227381477551</v>
+        <v>-14.7724614677551</v>
       </c>
       <c r="Q95">
-        <v>-10.9227381477551</v>
+        <v>-11.2724614677551</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.038161690889908</v>
+        <v>1.203555306038226</v>
       </c>
       <c r="T95">
-        <v>12.93379952784269</v>
+        <v>15.08943278248314</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08348318641297364</v>
+        <v>0.08259506740858029</v>
       </c>
       <c r="W95">
-        <v>0.1840365761682749</v>
+        <v>0.1842149104643571</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5565545760864909</v>
+        <v>0.5506337827238686</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2453753341987892</v>
+        <v>0.2469253341987891</v>
       </c>
       <c r="C96">
-        <v>-101.9407387120789</v>
+        <v>-104.6090846313412</v>
       </c>
       <c r="D96">
-        <v>80.36526128792107</v>
+        <v>79.74591536865881</v>
       </c>
       <c r="E96">
-        <v>81.506</v>
+        <v>83.55500000000001</v>
       </c>
       <c r="F96">
-        <v>192.606</v>
+        <v>194.655</v>
       </c>
       <c r="G96">
         <v>10.3</v>
@@ -9159,37 +9159,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M96">
-        <v>38.6752848</v>
+        <v>39.086724</v>
       </c>
       <c r="N96">
-        <v>-17.37936643265306</v>
+        <v>-17.79080563265306</v>
       </c>
       <c r="O96">
-        <v>-2.606904964897959</v>
+        <v>-2.66862084489796</v>
       </c>
       <c r="P96">
-        <v>-14.7724614677551</v>
+        <v>-15.1221847877551</v>
       </c>
       <c r="Q96">
-        <v>-11.2724614677551</v>
+        <v>-11.6221847877551</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.203555306038226</v>
+        <v>1.435106367245872</v>
       </c>
       <c r="T96">
-        <v>15.08943278248314</v>
+        <v>18.10731933897978</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.08259506740858029</v>
+        <v>0.0817256456463847</v>
       </c>
       <c r="W96">
-        <v>0.1842149104643571</v>
+        <v>0.184389490354206</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5506337827238686</v>
+        <v>0.5448376376425648</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2469253341987891</v>
+        <v>0.2484753341987892</v>
       </c>
       <c r="C97">
-        <v>-104.6090846313412</v>
+        <v>-107.2679574079672</v>
       </c>
       <c r="D97">
-        <v>79.74591536865881</v>
+        <v>79.13604259203278</v>
       </c>
       <c r="E97">
-        <v>83.55500000000001</v>
+        <v>85.60400000000001</v>
       </c>
       <c r="F97">
-        <v>194.655</v>
+        <v>196.704</v>
       </c>
       <c r="G97">
         <v>10.3</v>
@@ -9241,37 +9241,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M97">
-        <v>39.086724</v>
+        <v>39.4981632</v>
       </c>
       <c r="N97">
-        <v>-17.79080563265306</v>
+        <v>-18.20224483265306</v>
       </c>
       <c r="O97">
-        <v>-2.66862084489796</v>
+        <v>-2.730336724897959</v>
       </c>
       <c r="P97">
-        <v>-15.1221847877551</v>
+        <v>-15.4719081077551</v>
       </c>
       <c r="Q97">
-        <v>-11.6221847877551</v>
+        <v>-11.9719081077551</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.435106367245872</v>
+        <v>1.782432959057341</v>
       </c>
       <c r="T97">
-        <v>18.10731933897978</v>
+        <v>22.63414917372473</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.0817256456463847</v>
+        <v>0.0808743368375682</v>
       </c>
       <c r="W97">
-        <v>0.184389490354206</v>
+        <v>0.1845604331630163</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5448376376425648</v>
+        <v>0.539162245583788</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2484753341987892</v>
+        <v>0.2500253341987891</v>
       </c>
       <c r="C98">
-        <v>-107.2679574079672</v>
+        <v>-109.9175727356339</v>
       </c>
       <c r="D98">
-        <v>79.13604259203278</v>
+        <v>78.53542726436608</v>
       </c>
       <c r="E98">
-        <v>85.60399999999998</v>
+        <v>87.65299999999999</v>
       </c>
       <c r="F98">
-        <v>196.704</v>
+        <v>198.753</v>
       </c>
       <c r="G98">
         <v>10.3</v>
@@ -9323,37 +9323,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M98">
-        <v>39.4981632</v>
+        <v>39.9096024</v>
       </c>
       <c r="N98">
-        <v>-18.20224483265306</v>
+        <v>-18.61368403265306</v>
       </c>
       <c r="O98">
-        <v>-2.730336724897959</v>
+        <v>-2.792052604897959</v>
       </c>
       <c r="P98">
-        <v>-15.4719081077551</v>
+        <v>-15.8216314277551</v>
       </c>
       <c r="Q98">
-        <v>-11.9719081077551</v>
+        <v>-12.3216314277551</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.782432959057336</v>
+        <v>2.361310612076448</v>
       </c>
       <c r="T98">
-        <v>22.63414917372467</v>
+        <v>30.17886556496623</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.0808743368375682</v>
+        <v>0.08004058078769638</v>
       </c>
       <c r="W98">
-        <v>0.1845604331630163</v>
+        <v>0.1847278513778306</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.539162245583788</v>
+        <v>0.5336038719179759</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2500253341987891</v>
+        <v>0.2515753341987891</v>
       </c>
       <c r="C99">
-        <v>-109.9175727356339</v>
+        <v>-112.5581398091791</v>
       </c>
       <c r="D99">
-        <v>78.53542726436608</v>
+        <v>77.94386019082087</v>
       </c>
       <c r="E99">
-        <v>87.65299999999999</v>
+        <v>89.70199999999997</v>
       </c>
       <c r="F99">
-        <v>198.753</v>
+        <v>200.802</v>
       </c>
       <c r="G99">
         <v>10.3</v>
@@ -9405,37 +9405,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M99">
-        <v>39.9096024</v>
+        <v>40.32104159999999</v>
       </c>
       <c r="N99">
-        <v>-18.61368403265306</v>
+        <v>-19.02512323265305</v>
       </c>
       <c r="O99">
-        <v>-2.792052604897959</v>
+        <v>-2.853768484897958</v>
       </c>
       <c r="P99">
-        <v>-15.8216314277551</v>
+        <v>-16.1713547477551</v>
       </c>
       <c r="Q99">
-        <v>-12.3216314277551</v>
+        <v>-12.6713547477551</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.361310612076448</v>
+        <v>3.519065918114672</v>
       </c>
       <c r="T99">
-        <v>30.17886556496623</v>
+        <v>45.26829834744935</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08004058078769638</v>
+        <v>0.07922384016741375</v>
       </c>
       <c r="W99">
-        <v>0.1847278513778306</v>
+        <v>0.1848918528943833</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5336038719179759</v>
+        <v>0.5281589344494251</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2515753341987891</v>
+        <v>0.2531253341987891</v>
       </c>
       <c r="C100">
-        <v>-112.5581398091791</v>
+        <v>-115.1898615675337</v>
       </c>
       <c r="D100">
-        <v>77.94386019082087</v>
+        <v>77.36113843246628</v>
       </c>
       <c r="E100">
-        <v>89.70199999999997</v>
+        <v>91.75099999999998</v>
       </c>
       <c r="F100">
-        <v>200.802</v>
+        <v>202.851</v>
       </c>
       <c r="G100">
         <v>10.3</v>
@@ -9487,37 +9487,37 @@
         <v>21.29591836734694</v>
       </c>
       <c r="M100">
-        <v>40.32104159999999</v>
+        <v>40.7324808</v>
       </c>
       <c r="N100">
-        <v>-19.02512323265305</v>
+        <v>-19.43656243265306</v>
       </c>
       <c r="O100">
-        <v>-2.853768484897958</v>
+        <v>-2.915484364897959</v>
       </c>
       <c r="P100">
-        <v>-16.1713547477551</v>
+        <v>-16.5210780677551</v>
       </c>
       <c r="Q100">
-        <v>-12.6713547477551</v>
+        <v>-13.0210780677551</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.519065918114672</v>
+        <v>6.992331836229344</v>
       </c>
       <c r="T100">
-        <v>45.26829834744935</v>
+        <v>90.53659669489869</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07922384016741375</v>
+        <v>0.07842359935764188</v>
       </c>
       <c r="W100">
-        <v>0.1848918528943833</v>
+        <v>0.1850525412489855</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5281589344494251</v>
+        <v>0.5228239957176126</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2531253341987891</v>
-      </c>
-      <c r="C101">
-        <v>-115.1898615675337</v>
-      </c>
-      <c r="D101">
-        <v>77.36113843246628</v>
-      </c>
-      <c r="E101">
-        <v>91.75099999999998</v>
-      </c>
-      <c r="F101">
-        <v>202.851</v>
-      </c>
-      <c r="G101">
-        <v>10.3</v>
-      </c>
-      <c r="H101">
-        <v>93.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>24.79591836734694</v>
-      </c>
-      <c r="K101">
-        <v>3.5</v>
-      </c>
-      <c r="L101">
-        <v>21.29591836734694</v>
-      </c>
-      <c r="M101">
-        <v>40.7324808</v>
-      </c>
-      <c r="N101">
-        <v>-19.43656243265306</v>
-      </c>
-      <c r="O101">
-        <v>-2.915484364897959</v>
-      </c>
-      <c r="P101">
-        <v>-16.5210780677551</v>
-      </c>
-      <c r="Q101">
-        <v>-13.0210780677551</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.992331836229344</v>
-      </c>
-      <c r="T101">
-        <v>90.53659669489869</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.07842359935764188</v>
-      </c>
-      <c r="W101">
-        <v>0.1850525412489855</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5228239957176126</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
